--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F195"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4322,7 +4322,7 @@
         <v>60.70000076293945</v>
       </c>
       <c r="F194" t="n">
-        <v>290507</v>
+        <v>240044</v>
       </c>
     </row>
     <row r="195">
@@ -4330,19 +4330,219 @@
         <v>45936</v>
       </c>
       <c r="B195" t="n">
-        <v>61.70000076293945</v>
+        <v>61.68999862670898</v>
       </c>
       <c r="C195" t="n">
-        <v>61.91999816894531</v>
+        <v>62.11999893188477</v>
       </c>
       <c r="D195" t="n">
-        <v>61.09000015258789</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="E195" t="n">
         <v>61.13999938964844</v>
       </c>
       <c r="F195" t="n">
-        <v>26776</v>
+        <v>224682</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B196" t="n">
+        <v>61.72999954223633</v>
+      </c>
+      <c r="C196" t="n">
+        <v>62.11000061035156</v>
+      </c>
+      <c r="D196" t="n">
+        <v>60.72000122070312</v>
+      </c>
+      <c r="E196" t="n">
+        <v>61.72999954223633</v>
+      </c>
+      <c r="F196" t="n">
+        <v>245121</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B197" t="n">
+        <v>62.54999923706055</v>
+      </c>
+      <c r="C197" t="n">
+        <v>62.91999816894531</v>
+      </c>
+      <c r="D197" t="n">
+        <v>62.04999923706055</v>
+      </c>
+      <c r="E197" t="n">
+        <v>62.04999923706055</v>
+      </c>
+      <c r="F197" t="n">
+        <v>273318</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B198" t="n">
+        <v>61.5099983215332</v>
+      </c>
+      <c r="C198" t="n">
+        <v>62.86999893188477</v>
+      </c>
+      <c r="D198" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="E198" t="n">
+        <v>62.31000137329102</v>
+      </c>
+      <c r="F198" t="n">
+        <v>259171</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B199" t="n">
+        <v>58.90000152587891</v>
+      </c>
+      <c r="C199" t="n">
+        <v>61.66999816894531</v>
+      </c>
+      <c r="D199" t="n">
+        <v>58.22000122070312</v>
+      </c>
+      <c r="E199" t="n">
+        <v>61.4900016784668</v>
+      </c>
+      <c r="F199" t="n">
+        <v>339103</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B200" t="n">
+        <v>59.4900016784668</v>
+      </c>
+      <c r="C200" t="n">
+        <v>60.16999816894531</v>
+      </c>
+      <c r="D200" t="n">
+        <v>59</v>
+      </c>
+      <c r="E200" t="n">
+        <v>59</v>
+      </c>
+      <c r="F200" t="n">
+        <v>339103</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B201" t="n">
+        <v>58.70000076293945</v>
+      </c>
+      <c r="C201" t="n">
+        <v>59.81999969482422</v>
+      </c>
+      <c r="D201" t="n">
+        <v>57.68000030517578</v>
+      </c>
+      <c r="E201" t="n">
+        <v>59.58000183105469</v>
+      </c>
+      <c r="F201" t="n">
+        <v>259200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B202" t="n">
+        <v>58.27000045776367</v>
+      </c>
+      <c r="C202" t="n">
+        <v>59.41999816894531</v>
+      </c>
+      <c r="D202" t="n">
+        <v>58.20000076293945</v>
+      </c>
+      <c r="E202" t="n">
+        <v>58.59999847412109</v>
+      </c>
+      <c r="F202" t="n">
+        <v>224919</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B203" t="n">
+        <v>57.45999908447266</v>
+      </c>
+      <c r="C203" t="n">
+        <v>59.11000061035156</v>
+      </c>
+      <c r="D203" t="n">
+        <v>57.2599983215332</v>
+      </c>
+      <c r="E203" t="n">
+        <v>58.77000045776367</v>
+      </c>
+      <c r="F203" t="n">
+        <v>203866</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B204" t="n">
+        <v>57.54000091552734</v>
+      </c>
+      <c r="C204" t="n">
+        <v>57.72000122070312</v>
+      </c>
+      <c r="D204" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="E204" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F204" t="n">
+        <v>203866</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B205" t="n">
+        <v>57.06000137329102</v>
+      </c>
+      <c r="C205" t="n">
+        <v>57.81000137329102</v>
+      </c>
+      <c r="D205" t="n">
+        <v>56.95000076293945</v>
+      </c>
+      <c r="E205" t="n">
+        <v>57.72999954223633</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4151</v>
       </c>
     </row>
   </sheetData>

--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4522,7 +4522,7 @@
         <v>57.5</v>
       </c>
       <c r="F204" t="n">
-        <v>203866</v>
+        <v>108748</v>
       </c>
     </row>
     <row r="205">
@@ -4530,19 +4530,119 @@
         <v>45950</v>
       </c>
       <c r="B205" t="n">
-        <v>57.06000137329102</v>
+        <v>57.52000045776367</v>
       </c>
       <c r="C205" t="n">
         <v>57.81000137329102</v>
       </c>
       <c r="D205" t="n">
-        <v>56.95000076293945</v>
+        <v>56.34999847412109</v>
       </c>
       <c r="E205" t="n">
         <v>57.72999954223633</v>
       </c>
       <c r="F205" t="n">
-        <v>4151</v>
+        <v>108146</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B206" t="n">
+        <v>57.81999969482422</v>
+      </c>
+      <c r="C206" t="n">
+        <v>58.27999877929688</v>
+      </c>
+      <c r="D206" t="n">
+        <v>56.9900016784668</v>
+      </c>
+      <c r="E206" t="n">
+        <v>57.36999893188477</v>
+      </c>
+      <c r="F206" t="n">
+        <v>314207</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B207" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C207" t="n">
+        <v>59.83000183105469</v>
+      </c>
+      <c r="D207" t="n">
+        <v>57.34000015258789</v>
+      </c>
+      <c r="E207" t="n">
+        <v>57.59000015258789</v>
+      </c>
+      <c r="F207" t="n">
+        <v>378637</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B208" t="n">
+        <v>61.79000091552734</v>
+      </c>
+      <c r="C208" t="n">
+        <v>62.20000076293945</v>
+      </c>
+      <c r="D208" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="E208" t="n">
+        <v>59.93999862670898</v>
+      </c>
+      <c r="F208" t="n">
+        <v>735186</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B209" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C209" t="n">
+        <v>62.59000015258789</v>
+      </c>
+      <c r="D209" t="n">
+        <v>61.20999908447266</v>
+      </c>
+      <c r="E209" t="n">
+        <v>61.79000091552734</v>
+      </c>
+      <c r="F209" t="n">
+        <v>735186</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B210" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="C210" t="n">
+        <v>62.16999816894531</v>
+      </c>
+      <c r="D210" t="n">
+        <v>60.66999816894531</v>
+      </c>
+      <c r="E210" t="n">
+        <v>61.81999969482422</v>
+      </c>
+      <c r="F210" t="n">
+        <v>172792</v>
       </c>
     </row>
   </sheetData>

--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4622,7 +4622,7 @@
         <v>61.79000091552734</v>
       </c>
       <c r="F209" t="n">
-        <v>735186</v>
+        <v>373744</v>
       </c>
     </row>
     <row r="210">
@@ -4630,7 +4630,7 @@
         <v>45957</v>
       </c>
       <c r="B210" t="n">
-        <v>61.75</v>
+        <v>61.31000137329102</v>
       </c>
       <c r="C210" t="n">
         <v>62.16999816894531</v>
@@ -4642,7 +4642,327 @@
         <v>61.81999969482422</v>
       </c>
       <c r="F210" t="n">
-        <v>172792</v>
+        <v>272191</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B211" t="n">
+        <v>60.15000152587891</v>
+      </c>
+      <c r="C211" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D211" t="n">
+        <v>59.7599983215332</v>
+      </c>
+      <c r="E211" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F211" t="n">
+        <v>307568</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B212" t="n">
+        <v>60.47999954223633</v>
+      </c>
+      <c r="C212" t="n">
+        <v>61.02000045776367</v>
+      </c>
+      <c r="D212" t="n">
+        <v>59.70000076293945</v>
+      </c>
+      <c r="E212" t="n">
+        <v>60.18000030517578</v>
+      </c>
+      <c r="F212" t="n">
+        <v>276875</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B213" t="n">
+        <v>60.56999969482422</v>
+      </c>
+      <c r="C213" t="n">
+        <v>60.79000091552734</v>
+      </c>
+      <c r="D213" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="E213" t="n">
+        <v>60.38999938964844</v>
+      </c>
+      <c r="F213" t="n">
+        <v>247917</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B214" t="n">
+        <v>60.97999954223633</v>
+      </c>
+      <c r="C214" t="n">
+        <v>61.38000106811523</v>
+      </c>
+      <c r="D214" t="n">
+        <v>59.9900016784668</v>
+      </c>
+      <c r="E214" t="n">
+        <v>60.29999923706055</v>
+      </c>
+      <c r="F214" t="n">
+        <v>278598</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B215" t="n">
+        <v>61.04999923706055</v>
+      </c>
+      <c r="C215" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>60.5099983215332</v>
+      </c>
+      <c r="E215" t="n">
+        <v>61.40000152587891</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B216" t="n">
+        <v>60.56000137329102</v>
+      </c>
+      <c r="C216" t="n">
+        <v>61.02999877929688</v>
+      </c>
+      <c r="D216" t="n">
+        <v>59.93999862670898</v>
+      </c>
+      <c r="E216" t="n">
+        <v>61.02999877929688</v>
+      </c>
+      <c r="F216" t="n">
+        <v>219300</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B217" t="n">
+        <v>59.59999847412109</v>
+      </c>
+      <c r="C217" t="n">
+        <v>61.09000015258789</v>
+      </c>
+      <c r="D217" t="n">
+        <v>59.52000045776367</v>
+      </c>
+      <c r="E217" t="n">
+        <v>60.43000030517578</v>
+      </c>
+      <c r="F217" t="n">
+        <v>292518</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B218" t="n">
+        <v>59.43000030517578</v>
+      </c>
+      <c r="C218" t="n">
+        <v>60.5099983215332</v>
+      </c>
+      <c r="D218" t="n">
+        <v>58.83000183105469</v>
+      </c>
+      <c r="E218" t="n">
+        <v>59.68000030517578</v>
+      </c>
+      <c r="F218" t="n">
+        <v>277768</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B219" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="C219" t="n">
+        <v>60.45999908447266</v>
+      </c>
+      <c r="D219" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="E219" t="n">
+        <v>59.65000152587891</v>
+      </c>
+      <c r="F219" t="n">
+        <v>259446</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B220" t="n">
+        <v>60.13000106811523</v>
+      </c>
+      <c r="C220" t="n">
+        <v>60.47999954223633</v>
+      </c>
+      <c r="D220" t="n">
+        <v>59.40999984741211</v>
+      </c>
+      <c r="E220" t="n">
+        <v>59.86999893188477</v>
+      </c>
+      <c r="F220" t="n">
+        <v>222879</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B221" t="n">
+        <v>61.04000091552734</v>
+      </c>
+      <c r="C221" t="n">
+        <v>61.27999877929688</v>
+      </c>
+      <c r="D221" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="E221" t="n">
+        <v>60.06999969482422</v>
+      </c>
+      <c r="F221" t="n">
+        <v>264427</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B222" t="n">
+        <v>58.4900016784668</v>
+      </c>
+      <c r="C222" t="n">
+        <v>61.06000137329102</v>
+      </c>
+      <c r="D222" t="n">
+        <v>58.29999923706055</v>
+      </c>
+      <c r="E222" t="n">
+        <v>61.04999923706055</v>
+      </c>
+      <c r="F222" t="n">
+        <v>329517</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B223" t="n">
+        <v>58.68999862670898</v>
+      </c>
+      <c r="C223" t="n">
+        <v>59.20999908447266</v>
+      </c>
+      <c r="D223" t="n">
+        <v>58.11999893188477</v>
+      </c>
+      <c r="E223" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="F223" t="n">
+        <v>247349</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B224" t="n">
+        <v>60.09000015258789</v>
+      </c>
+      <c r="C224" t="n">
+        <v>60.65000152587891</v>
+      </c>
+      <c r="D224" t="n">
+        <v>58.70999908447266</v>
+      </c>
+      <c r="E224" t="n">
+        <v>58.70999908447266</v>
+      </c>
+      <c r="F224" t="n">
+        <v>334116</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B225" t="n">
+        <v>59.90999984741211</v>
+      </c>
+      <c r="C225" t="n">
+        <v>60.43999862670898</v>
+      </c>
+      <c r="D225" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="E225" t="n">
+        <v>59.79999923706055</v>
+      </c>
+      <c r="F225" t="n">
+        <v>334116</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B226" t="n">
+        <v>59.29999923706055</v>
+      </c>
+      <c r="C226" t="n">
+        <v>59.86000061035156</v>
+      </c>
+      <c r="D226" t="n">
+        <v>59.33000183105469</v>
+      </c>
+      <c r="E226" t="n">
+        <v>59.7400016784668</v>
+      </c>
+      <c r="F226" t="n">
+        <v>14574</v>
       </c>
     </row>
   </sheetData>

--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F226"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4942,7 +4942,7 @@
         <v>59.79999923706055</v>
       </c>
       <c r="F225" t="n">
-        <v>334116</v>
+        <v>189638</v>
       </c>
     </row>
     <row r="226">
@@ -4950,19 +4950,519 @@
         <v>45979</v>
       </c>
       <c r="B226" t="n">
-        <v>59.29999923706055</v>
+        <v>60.7400016784668</v>
       </c>
       <c r="C226" t="n">
-        <v>59.86000061035156</v>
+        <v>60.93000030517578</v>
       </c>
       <c r="D226" t="n">
-        <v>59.33000183105469</v>
+        <v>59.31000137329102</v>
       </c>
       <c r="E226" t="n">
         <v>59.7400016784668</v>
       </c>
       <c r="F226" t="n">
-        <v>14574</v>
+        <v>105325</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B227" t="n">
+        <v>59.43999862670898</v>
+      </c>
+      <c r="C227" t="n">
+        <v>60.79000091552734</v>
+      </c>
+      <c r="D227" t="n">
+        <v>58.77000045776367</v>
+      </c>
+      <c r="E227" t="n">
+        <v>60.61999893188477</v>
+      </c>
+      <c r="F227" t="n">
+        <v>79622</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B228" t="n">
+        <v>59.13999938964844</v>
+      </c>
+      <c r="C228" t="n">
+        <v>60.33000183105469</v>
+      </c>
+      <c r="D228" t="n">
+        <v>58.86000061035156</v>
+      </c>
+      <c r="E228" t="n">
+        <v>59.63000106811523</v>
+      </c>
+      <c r="F228" t="n">
+        <v>324282</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B229" t="n">
+        <v>58.06000137329102</v>
+      </c>
+      <c r="C229" t="n">
+        <v>58.79999923706055</v>
+      </c>
+      <c r="D229" t="n">
+        <v>57.38000106811523</v>
+      </c>
+      <c r="E229" t="n">
+        <v>58.79999923706055</v>
+      </c>
+      <c r="F229" t="n">
+        <v>345014</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B230" t="n">
+        <v>58.84000015258789</v>
+      </c>
+      <c r="C230" t="n">
+        <v>59.06000137329102</v>
+      </c>
+      <c r="D230" t="n">
+        <v>57.41999816894531</v>
+      </c>
+      <c r="E230" t="n">
+        <v>58.04999923706055</v>
+      </c>
+      <c r="F230" t="n">
+        <v>238138</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B231" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="C231" t="n">
+        <v>58.95999908447266</v>
+      </c>
+      <c r="D231" t="n">
+        <v>57.09999847412109</v>
+      </c>
+      <c r="E231" t="n">
+        <v>58.88999938964844</v>
+      </c>
+      <c r="F231" t="n">
+        <v>334442</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B232" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="C232" t="n">
+        <v>58.72000122070312</v>
+      </c>
+      <c r="D232" t="n">
+        <v>57.65999984741211</v>
+      </c>
+      <c r="E232" t="n">
+        <v>58.04999923706055</v>
+      </c>
+      <c r="F232" t="n">
+        <v>228285</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B233" t="n">
+        <v>58.54999923706055</v>
+      </c>
+      <c r="C233" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="D233" t="n">
+        <v>58.27000045776367</v>
+      </c>
+      <c r="E233" t="n">
+        <v>58.58000183105469</v>
+      </c>
+      <c r="F233" t="n">
+        <v>153758</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B234" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="C234" t="n">
+        <v>59.97000122070312</v>
+      </c>
+      <c r="D234" t="n">
+        <v>58.83000183105469</v>
+      </c>
+      <c r="E234" t="n">
+        <v>58.95999908447266</v>
+      </c>
+      <c r="F234" t="n">
+        <v>232770</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B235" t="n">
+        <v>58.63999938964844</v>
+      </c>
+      <c r="C235" t="n">
+        <v>59.66999816894531</v>
+      </c>
+      <c r="D235" t="n">
+        <v>58.27999877929688</v>
+      </c>
+      <c r="E235" t="n">
+        <v>59.52000045776367</v>
+      </c>
+      <c r="F235" t="n">
+        <v>255513</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B236" t="n">
+        <v>58.95000076293945</v>
+      </c>
+      <c r="C236" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="D236" t="n">
+        <v>58.36999893188477</v>
+      </c>
+      <c r="E236" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="F236" t="n">
+        <v>260974</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B237" t="n">
+        <v>59.66999816894531</v>
+      </c>
+      <c r="C237" t="n">
+        <v>60.02000045776367</v>
+      </c>
+      <c r="D237" t="n">
+        <v>58.81000137329102</v>
+      </c>
+      <c r="E237" t="n">
+        <v>59.09000015258789</v>
+      </c>
+      <c r="F237" t="n">
+        <v>264993</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B238" t="n">
+        <v>60.08000183105469</v>
+      </c>
+      <c r="C238" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D238" t="n">
+        <v>59.41999816894531</v>
+      </c>
+      <c r="E238" t="n">
+        <v>59.70000076293945</v>
+      </c>
+      <c r="F238" t="n">
+        <v>255075</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B239" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="C239" t="n">
+        <v>60.29999923706055</v>
+      </c>
+      <c r="D239" t="n">
+        <v>58.68000030517578</v>
+      </c>
+      <c r="E239" t="n">
+        <v>60.15000152587891</v>
+      </c>
+      <c r="F239" t="n">
+        <v>263009</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B240" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="C240" t="n">
+        <v>59.16999816894531</v>
+      </c>
+      <c r="D240" t="n">
+        <v>58.11999893188477</v>
+      </c>
+      <c r="E240" t="n">
+        <v>58.86999893188477</v>
+      </c>
+      <c r="F240" t="n">
+        <v>260206</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B241" t="n">
+        <v>58.45999908447266</v>
+      </c>
+      <c r="C241" t="n">
+        <v>59.04999923706055</v>
+      </c>
+      <c r="D241" t="n">
+        <v>57.65999984741211</v>
+      </c>
+      <c r="E241" t="n">
+        <v>58.36999893188477</v>
+      </c>
+      <c r="F241" t="n">
+        <v>256508</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B242" t="n">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="C242" t="n">
+        <v>58.93999862670898</v>
+      </c>
+      <c r="D242" t="n">
+        <v>57.0099983215332</v>
+      </c>
+      <c r="E242" t="n">
+        <v>58.90999984741211</v>
+      </c>
+      <c r="F242" t="n">
+        <v>286808</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B243" t="n">
+        <v>57.43999862670898</v>
+      </c>
+      <c r="C243" t="n">
+        <v>58.18999862670898</v>
+      </c>
+      <c r="D243" t="n">
+        <v>57.15000152587891</v>
+      </c>
+      <c r="E243" t="n">
+        <v>57.88999938964844</v>
+      </c>
+      <c r="F243" t="n">
+        <v>212806</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B244" t="n">
+        <v>56.81999969482422</v>
+      </c>
+      <c r="C244" t="n">
+        <v>57.79999923706055</v>
+      </c>
+      <c r="D244" t="n">
+        <v>56.40000152587891</v>
+      </c>
+      <c r="E244" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F244" t="n">
+        <v>229310</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B245" t="n">
+        <v>55.27000045776367</v>
+      </c>
+      <c r="C245" t="n">
+        <v>56.70000076293945</v>
+      </c>
+      <c r="D245" t="n">
+        <v>54.97999954223633</v>
+      </c>
+      <c r="E245" t="n">
+        <v>56.68000030517578</v>
+      </c>
+      <c r="F245" t="n">
+        <v>230933</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B246" t="n">
+        <v>55.93999862670898</v>
+      </c>
+      <c r="C246" t="n">
+        <v>56.97999954223633</v>
+      </c>
+      <c r="D246" t="n">
+        <v>55.20000076293945</v>
+      </c>
+      <c r="E246" t="n">
+        <v>55.22999954223633</v>
+      </c>
+      <c r="F246" t="n">
+        <v>125608</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B247" t="n">
+        <v>56.15000152587891</v>
+      </c>
+      <c r="C247" t="n">
+        <v>57.02999877929688</v>
+      </c>
+      <c r="D247" t="n">
+        <v>55.88000106811523</v>
+      </c>
+      <c r="E247" t="n">
+        <v>56.90000152587891</v>
+      </c>
+      <c r="F247" t="n">
+        <v>85735</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B248" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="C248" t="n">
+        <v>56.90000152587891</v>
+      </c>
+      <c r="D248" t="n">
+        <v>55.81999969482422</v>
+      </c>
+      <c r="E248" t="n">
+        <v>56.02999877929688</v>
+      </c>
+      <c r="F248" t="n">
+        <v>209264</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B249" t="n">
+        <v>58.0099983215332</v>
+      </c>
+      <c r="C249" t="n">
+        <v>58.13000106811523</v>
+      </c>
+      <c r="D249" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="E249" t="n">
+        <v>56.63000106811523</v>
+      </c>
+      <c r="F249" t="n">
+        <v>221576</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B250" t="n">
+        <v>58.38000106811523</v>
+      </c>
+      <c r="C250" t="n">
+        <v>58.56000137329102</v>
+      </c>
+      <c r="D250" t="n">
+        <v>57.7400016784668</v>
+      </c>
+      <c r="E250" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F250" t="n">
+        <v>183633</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B251" t="n">
+        <v>58.34999847412109</v>
+      </c>
+      <c r="C251" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="D251" t="n">
+        <v>58.13000106811523</v>
+      </c>
+      <c r="E251" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="F251" t="n">
+        <v>183633</v>
       </c>
     </row>
   </sheetData>

--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5462,7 +5462,67 @@
         <v>58.47000122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>183633</v>
+        <v>111762</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B252" t="n">
+        <v>56.7400016784668</v>
+      </c>
+      <c r="C252" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="D252" t="n">
+        <v>56.65000152587891</v>
+      </c>
+      <c r="E252" t="n">
+        <v>58.34999847412109</v>
+      </c>
+      <c r="F252" t="n">
+        <v>166669</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B253" t="n">
+        <v>58.08000183105469</v>
+      </c>
+      <c r="C253" t="n">
+        <v>58.29999923706055</v>
+      </c>
+      <c r="D253" t="n">
+        <v>56.90999984741211</v>
+      </c>
+      <c r="E253" t="n">
+        <v>57.04000091552734</v>
+      </c>
+      <c r="F253" t="n">
+        <v>178590</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B254" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="C254" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="D254" t="n">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="E254" t="n">
+        <v>57.81000137329102</v>
+      </c>
+      <c r="F254" t="n">
+        <v>143802</v>
       </c>
     </row>
   </sheetData>

--- a/crude_oil_2025.xlsx
+++ b/crude_oil_2025.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,401 +507,5441 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46024</v>
+        <v>45659</v>
       </c>
       <c r="B4" t="n">
-        <v>57.31999969482422</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="C4" t="n">
-        <v>57.93000030517578</v>
+        <v>73.73000335693359</v>
       </c>
       <c r="D4" t="n">
-        <v>56.59999847412109</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="E4" t="n">
-        <v>57.40999984741211</v>
+        <v>71.84999847412109</v>
       </c>
       <c r="F4" t="n">
-        <v>189503</v>
+        <v>306498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46027</v>
+        <v>45660</v>
       </c>
       <c r="B5" t="n">
-        <v>58.31999969482422</v>
+        <v>73.95999908447266</v>
       </c>
       <c r="C5" t="n">
-        <v>58.5099983215332</v>
+        <v>74.34999847412109</v>
       </c>
       <c r="D5" t="n">
-        <v>56.31000137329102</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="E5" t="n">
-        <v>57.47000122070312</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="F5" t="n">
-        <v>301483</v>
+        <v>296040</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46028</v>
+        <v>45663</v>
       </c>
       <c r="B6" t="n">
-        <v>57.13000106811523</v>
+        <v>73.55999755859375</v>
       </c>
       <c r="C6" t="n">
-        <v>58.86999893188477</v>
+        <v>74.98999786376953</v>
       </c>
       <c r="D6" t="n">
-        <v>56.84000015258789</v>
+        <v>73.19999694824219</v>
       </c>
       <c r="E6" t="n">
-        <v>58.34000015258789</v>
+        <v>74.05000305175781</v>
       </c>
       <c r="F6" t="n">
-        <v>292067</v>
+        <v>306042</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46029</v>
+        <v>45664</v>
       </c>
       <c r="B7" t="n">
-        <v>55.9900016784668</v>
+        <v>74.25</v>
       </c>
       <c r="C7" t="n">
-        <v>57.16999816894531</v>
+        <v>74.52999877929688</v>
       </c>
       <c r="D7" t="n">
-        <v>55.7599983215332</v>
+        <v>73.11000061035156</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>73.44000244140625</v>
       </c>
       <c r="F7" t="n">
-        <v>383128</v>
+        <v>277328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46030</v>
+        <v>45665</v>
       </c>
       <c r="B8" t="n">
-        <v>57.7599983215332</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7400016784668</v>
+        <v>75.29000091552734</v>
       </c>
       <c r="D8" t="n">
-        <v>55.97000122070312</v>
+        <v>73.16000366210938</v>
       </c>
       <c r="E8" t="n">
-        <v>56.41999816894531</v>
+        <v>74.51999664306641</v>
       </c>
       <c r="F8" t="n">
-        <v>334134</v>
+        <v>328617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46031</v>
+        <v>45666</v>
       </c>
       <c r="B9" t="n">
-        <v>59.11999893188477</v>
+        <v>73.91999816894531</v>
       </c>
       <c r="C9" t="n">
-        <v>59.77000045776367</v>
+        <v>74.31999969482422</v>
       </c>
       <c r="D9" t="n">
-        <v>57.61000061035156</v>
+        <v>72.83999633789062</v>
       </c>
       <c r="E9" t="n">
-        <v>58.40000152587891</v>
+        <v>73.31999969482422</v>
       </c>
       <c r="F9" t="n">
-        <v>360309</v>
+        <v>213421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46034</v>
+        <v>45667</v>
       </c>
       <c r="B10" t="n">
-        <v>59.5</v>
+        <v>76.56999969482422</v>
       </c>
       <c r="C10" t="n">
-        <v>59.90999984741211</v>
+        <v>77.86000061035156</v>
       </c>
       <c r="D10" t="n">
-        <v>58.45000076293945</v>
+        <v>74.01999664306641</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>74.29000091552734</v>
       </c>
       <c r="F10" t="n">
-        <v>309700</v>
+        <v>478432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46035</v>
+        <v>45670</v>
       </c>
       <c r="B11" t="n">
-        <v>61.15000152587891</v>
+        <v>78.81999969482422</v>
       </c>
       <c r="C11" t="n">
-        <v>61.5</v>
+        <v>79.26999664306641</v>
       </c>
       <c r="D11" t="n">
-        <v>59.47000122070312</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="E11" t="n">
-        <v>59.95000076293945</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="F11" t="n">
-        <v>411190</v>
+        <v>460942</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46036</v>
+        <v>45671</v>
       </c>
       <c r="B12" t="n">
-        <v>62.02000045776367</v>
+        <v>77.5</v>
       </c>
       <c r="C12" t="n">
-        <v>62.36000061035156</v>
+        <v>79.08999633789062</v>
       </c>
       <c r="D12" t="n">
-        <v>59.18999862670898</v>
+        <v>77.41000366210938</v>
       </c>
       <c r="E12" t="n">
-        <v>61.11999893188477</v>
+        <v>78.81999969482422</v>
       </c>
       <c r="F12" t="n">
-        <v>410261</v>
+        <v>326729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46037</v>
+        <v>45672</v>
       </c>
       <c r="B13" t="n">
-        <v>59.18999862670898</v>
+        <v>80.04000091552734</v>
       </c>
       <c r="C13" t="n">
-        <v>61.13999938964844</v>
+        <v>80.76999664306641</v>
       </c>
       <c r="D13" t="n">
-        <v>58.88000106811523</v>
+        <v>77.23999786376953</v>
       </c>
       <c r="E13" t="n">
-        <v>61.06000137329102</v>
+        <v>78.02999877929688</v>
       </c>
       <c r="F13" t="n">
-        <v>113642</v>
+        <v>321422</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46038</v>
+        <v>45673</v>
       </c>
       <c r="B14" t="n">
-        <v>59.43999862670898</v>
+        <v>78.68000030517578</v>
       </c>
       <c r="C14" t="n">
-        <v>60.18000030517578</v>
+        <v>80.58999633789062</v>
       </c>
       <c r="D14" t="n">
-        <v>58.93999862670898</v>
+        <v>77.87000274658203</v>
       </c>
       <c r="E14" t="n">
-        <v>59.2599983215332</v>
+        <v>80.40000152587891</v>
       </c>
       <c r="F14" t="n">
-        <v>113794</v>
+        <v>159948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46042</v>
+        <v>45674</v>
       </c>
       <c r="B15" t="n">
-        <v>60.34000015258789</v>
+        <v>77.87999725341797</v>
       </c>
       <c r="C15" t="n">
-        <v>60.68000030517578</v>
+        <v>79.44000244140625</v>
       </c>
       <c r="D15" t="n">
-        <v>58.70000076293945</v>
+        <v>77.76000213623047</v>
       </c>
       <c r="E15" t="n">
-        <v>59.0099983215332</v>
+        <v>78.75</v>
       </c>
       <c r="F15" t="n">
-        <v>499595</v>
+        <v>112409</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46043</v>
+        <v>45678</v>
       </c>
       <c r="B16" t="n">
-        <v>60.61999893188477</v>
+        <v>75.88999938964844</v>
       </c>
       <c r="C16" t="n">
-        <v>60.88999938964844</v>
+        <v>78.47000122070312</v>
       </c>
       <c r="D16" t="n">
-        <v>59.22000122070312</v>
+        <v>75.48999786376953</v>
       </c>
       <c r="E16" t="n">
-        <v>59.56999969482422</v>
+        <v>78.19000244140625</v>
       </c>
       <c r="F16" t="n">
-        <v>333062</v>
+        <v>568807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46044</v>
+        <v>45679</v>
       </c>
       <c r="B17" t="n">
-        <v>59.36000061035156</v>
+        <v>75.44000244140625</v>
       </c>
       <c r="C17" t="n">
-        <v>60.81999969482422</v>
+        <v>76.44999694824219</v>
       </c>
       <c r="D17" t="n">
-        <v>58.95999908447266</v>
+        <v>75.27999877929688</v>
       </c>
       <c r="E17" t="n">
-        <v>60.68000030517578</v>
+        <v>75.87999725341797</v>
       </c>
       <c r="F17" t="n">
-        <v>324349</v>
+        <v>315333</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46045</v>
+        <v>45680</v>
       </c>
       <c r="B18" t="n">
-        <v>61.06999969482422</v>
+        <v>74.62000274658203</v>
       </c>
       <c r="C18" t="n">
-        <v>61.36000061035156</v>
+        <v>76</v>
       </c>
       <c r="D18" t="n">
-        <v>59.52000045776367</v>
+        <v>74.13999938964844</v>
       </c>
       <c r="E18" t="n">
-        <v>59.65999984741211</v>
+        <v>75.38999938964844</v>
       </c>
       <c r="F18" t="n">
-        <v>283419</v>
+        <v>350688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46048</v>
+        <v>45681</v>
       </c>
       <c r="B19" t="n">
-        <v>60.63000106811523</v>
+        <v>74.66000366210938</v>
       </c>
       <c r="C19" t="n">
-        <v>61.70999908447266</v>
+        <v>75.20999908447266</v>
       </c>
       <c r="D19" t="n">
-        <v>60.31999969482422</v>
+        <v>74.01000213623047</v>
       </c>
       <c r="E19" t="n">
-        <v>61.22000122070312</v>
+        <v>74.30000305175781</v>
       </c>
       <c r="F19" t="n">
-        <v>281062</v>
+        <v>319679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46049</v>
+        <v>45684</v>
       </c>
       <c r="B20" t="n">
-        <v>62.38999938964844</v>
+        <v>73.16999816894531</v>
       </c>
       <c r="C20" t="n">
-        <v>62.63000106811523</v>
+        <v>75.15000152587891</v>
       </c>
       <c r="D20" t="n">
-        <v>60.13999938964844</v>
+        <v>72.37999725341797</v>
       </c>
       <c r="E20" t="n">
-        <v>60.77999877929688</v>
+        <v>74.54000091552734</v>
       </c>
       <c r="F20" t="n">
-        <v>360208</v>
+        <v>334418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46050</v>
+        <v>45685</v>
       </c>
       <c r="B21" t="n">
-        <v>63.20999908447266</v>
+        <v>73.76999664306641</v>
       </c>
       <c r="C21" t="n">
-        <v>63.56999969482422</v>
+        <v>74.30999755859375</v>
       </c>
       <c r="D21" t="n">
-        <v>62.06999969482422</v>
+        <v>72.93000030517578</v>
       </c>
       <c r="E21" t="n">
-        <v>62.58000183105469</v>
+        <v>73.15000152587891</v>
       </c>
       <c r="F21" t="n">
-        <v>354864</v>
+        <v>326075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46051</v>
+        <v>45686</v>
       </c>
       <c r="B22" t="n">
-        <v>65.41999816894531</v>
+        <v>72.62000274658203</v>
       </c>
       <c r="C22" t="n">
-        <v>66.48000335693359</v>
+        <v>74.08000183105469</v>
       </c>
       <c r="D22" t="n">
-        <v>63.27999877929688</v>
+        <v>72.33000183105469</v>
       </c>
       <c r="E22" t="n">
-        <v>63.5</v>
+        <v>73.94999694824219</v>
       </c>
       <c r="F22" t="n">
-        <v>560007</v>
+        <v>312733</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B23" t="n">
+        <v>72.73000335693359</v>
+      </c>
+      <c r="C23" t="n">
+        <v>73.83999633789062</v>
+      </c>
+      <c r="D23" t="n">
+        <v>72.01999664306641</v>
+      </c>
+      <c r="E23" t="n">
+        <v>73</v>
+      </c>
+      <c r="F23" t="n">
+        <v>336475</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B24" t="n">
+        <v>72.52999877929688</v>
+      </c>
+      <c r="C24" t="n">
+        <v>73.83999633789062</v>
+      </c>
+      <c r="D24" t="n">
+        <v>71.94000244140625</v>
+      </c>
+      <c r="E24" t="n">
+        <v>73.19999694824219</v>
+      </c>
+      <c r="F24" t="n">
+        <v>376335</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B25" t="n">
+        <v>73.16000366210938</v>
+      </c>
+      <c r="C25" t="n">
+        <v>75.18000030517578</v>
+      </c>
+      <c r="D25" t="n">
+        <v>72.05000305175781</v>
+      </c>
+      <c r="E25" t="n">
+        <v>74.13999938964844</v>
+      </c>
+      <c r="F25" t="n">
+        <v>517853</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B26" t="n">
+        <v>72.69999694824219</v>
+      </c>
+      <c r="C26" t="n">
+        <v>73.34999847412109</v>
+      </c>
+      <c r="D26" t="n">
+        <v>70.66999816894531</v>
+      </c>
+      <c r="E26" t="n">
+        <v>72.34999847412109</v>
+      </c>
+      <c r="F26" t="n">
+        <v>452961</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B27" t="n">
+        <v>71.02999877929688</v>
+      </c>
+      <c r="C27" t="n">
+        <v>72.97000122070312</v>
+      </c>
+      <c r="D27" t="n">
+        <v>70.95999908447266</v>
+      </c>
+      <c r="E27" t="n">
+        <v>72.76000213623047</v>
+      </c>
+      <c r="F27" t="n">
+        <v>289902</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B28" t="n">
+        <v>70.61000061035156</v>
+      </c>
+      <c r="C28" t="n">
+        <v>71.84999847412109</v>
+      </c>
+      <c r="D28" t="n">
+        <v>70.43000030517578</v>
+      </c>
+      <c r="E28" t="n">
+        <v>71.18000030517578</v>
+      </c>
+      <c r="F28" t="n">
+        <v>299037</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B29" t="n">
+        <v>71</v>
+      </c>
+      <c r="C29" t="n">
+        <v>71.41000366210938</v>
+      </c>
+      <c r="D29" t="n">
+        <v>70.47000122070312</v>
+      </c>
+      <c r="E29" t="n">
+        <v>70.55999755859375</v>
+      </c>
+      <c r="F29" t="n">
+        <v>273766</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B30" t="n">
+        <v>72.31999969482422</v>
+      </c>
+      <c r="C30" t="n">
+        <v>72.54000091552734</v>
+      </c>
+      <c r="D30" t="n">
+        <v>70.83999633789062</v>
+      </c>
+      <c r="E30" t="n">
+        <v>71</v>
+      </c>
+      <c r="F30" t="n">
+        <v>255941</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B31" t="n">
+        <v>73.31999969482422</v>
+      </c>
+      <c r="C31" t="n">
+        <v>73.68000030517578</v>
+      </c>
+      <c r="D31" t="n">
+        <v>72.30999755859375</v>
+      </c>
+      <c r="E31" t="n">
+        <v>72.48999786376953</v>
+      </c>
+      <c r="F31" t="n">
+        <v>266819</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B32" t="n">
+        <v>71.37000274658203</v>
+      </c>
+      <c r="C32" t="n">
+        <v>73.22000122070312</v>
+      </c>
+      <c r="D32" t="n">
+        <v>71.16999816894531</v>
+      </c>
+      <c r="E32" t="n">
+        <v>73.19999694824219</v>
+      </c>
+      <c r="F32" t="n">
+        <v>318123</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B33" t="n">
+        <v>71.29000091552734</v>
+      </c>
+      <c r="C33" t="n">
+        <v>71.59999847412109</v>
+      </c>
+      <c r="D33" t="n">
+        <v>70.22000122070312</v>
+      </c>
+      <c r="E33" t="n">
+        <v>71.23999786376953</v>
+      </c>
+      <c r="F33" t="n">
+        <v>278197</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B34" t="n">
+        <v>70.73999786376953</v>
+      </c>
+      <c r="C34" t="n">
+        <v>72.01999664306641</v>
+      </c>
+      <c r="D34" t="n">
+        <v>70.51999664306641</v>
+      </c>
+      <c r="E34" t="n">
+        <v>71.51999664306641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>207719</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B35" t="n">
+        <v>71.84999847412109</v>
+      </c>
+      <c r="C35" t="n">
+        <v>72.06999969482422</v>
+      </c>
+      <c r="D35" t="n">
+        <v>70.12000274658203</v>
+      </c>
+      <c r="E35" t="n">
+        <v>70.69999694824219</v>
+      </c>
+      <c r="F35" t="n">
+        <v>130937</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B36" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="C36" t="n">
+        <v>73.04000091552734</v>
+      </c>
+      <c r="D36" t="n">
+        <v>71.70999908447266</v>
+      </c>
+      <c r="E36" t="n">
+        <v>71.77999877929688</v>
+      </c>
+      <c r="F36" t="n">
+        <v>69012</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B37" t="n">
+        <v>72.56999969482422</v>
+      </c>
+      <c r="C37" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="D37" t="n">
+        <v>71.84999847412109</v>
+      </c>
+      <c r="E37" t="n">
+        <v>72.18000030517578</v>
+      </c>
+      <c r="F37" t="n">
+        <v>240060</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B38" t="n">
+        <v>70.40000152587891</v>
+      </c>
+      <c r="C38" t="n">
+        <v>72.76999664306641</v>
+      </c>
+      <c r="D38" t="n">
+        <v>70.16999816894531</v>
+      </c>
+      <c r="E38" t="n">
+        <v>72.58000183105469</v>
+      </c>
+      <c r="F38" t="n">
+        <v>268470</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B39" t="n">
+        <v>70.69999694824219</v>
+      </c>
+      <c r="C39" t="n">
+        <v>70.94000244140625</v>
+      </c>
+      <c r="D39" t="n">
+        <v>69.80000305175781</v>
+      </c>
+      <c r="E39" t="n">
+        <v>69.80000305175781</v>
+      </c>
+      <c r="F39" t="n">
+        <v>205468</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B40" t="n">
+        <v>68.93000030517578</v>
+      </c>
+      <c r="C40" t="n">
+        <v>71.26000213623047</v>
+      </c>
+      <c r="D40" t="n">
+        <v>68.68000030517578</v>
+      </c>
+      <c r="E40" t="n">
+        <v>70.91999816894531</v>
+      </c>
+      <c r="F40" t="n">
+        <v>267310</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>68.62000274658203</v>
+      </c>
+      <c r="C41" t="n">
+        <v>69.27999877929688</v>
+      </c>
+      <c r="D41" t="n">
+        <v>68.36000061035156</v>
+      </c>
+      <c r="E41" t="n">
+        <v>69.11000061035156</v>
+      </c>
+      <c r="F41" t="n">
+        <v>255601</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B42" t="n">
+        <v>70.34999847412109</v>
+      </c>
+      <c r="C42" t="n">
+        <v>70.54000091552734</v>
+      </c>
+      <c r="D42" t="n">
+        <v>68.61000061035156</v>
+      </c>
+      <c r="E42" t="n">
+        <v>68.81999969482422</v>
+      </c>
+      <c r="F42" t="n">
+        <v>265933</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B43" t="n">
+        <v>69.76000213623047</v>
+      </c>
+      <c r="C43" t="n">
+        <v>70.29000091552734</v>
+      </c>
+      <c r="D43" t="n">
+        <v>69.13999938964844</v>
+      </c>
+      <c r="E43" t="n">
+        <v>70.16999816894531</v>
+      </c>
+      <c r="F43" t="n">
+        <v>250074</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B44" t="n">
+        <v>68.37000274658203</v>
+      </c>
+      <c r="C44" t="n">
+        <v>70.59999847412109</v>
+      </c>
+      <c r="D44" t="n">
+        <v>67.88999938964844</v>
+      </c>
+      <c r="E44" t="n">
+        <v>69.94999694824219</v>
+      </c>
+      <c r="F44" t="n">
+        <v>332751</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B45" t="n">
+        <v>68.26000213623047</v>
+      </c>
+      <c r="C45" t="n">
+        <v>68.55999755859375</v>
+      </c>
+      <c r="D45" t="n">
+        <v>66.76999664306641</v>
+      </c>
+      <c r="E45" t="n">
+        <v>68.45999908447266</v>
+      </c>
+      <c r="F45" t="n">
+        <v>386750</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B46" t="n">
+        <v>66.30999755859375</v>
+      </c>
+      <c r="C46" t="n">
+        <v>68.09999847412109</v>
+      </c>
+      <c r="D46" t="n">
+        <v>65.22000122070312</v>
+      </c>
+      <c r="E46" t="n">
+        <v>68.08000183105469</v>
+      </c>
+      <c r="F46" t="n">
+        <v>382493</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B47" t="n">
+        <v>66.36000061035156</v>
+      </c>
+      <c r="C47" t="n">
+        <v>67.08999633789062</v>
+      </c>
+      <c r="D47" t="n">
+        <v>65.58999633789062</v>
+      </c>
+      <c r="E47" t="n">
+        <v>66.38999938964844</v>
+      </c>
+      <c r="F47" t="n">
+        <v>341632</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B48" t="n">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="C48" t="n">
+        <v>68.22000122070312</v>
+      </c>
+      <c r="D48" t="n">
+        <v>66.12000274658203</v>
+      </c>
+      <c r="E48" t="n">
+        <v>66.33999633789062</v>
+      </c>
+      <c r="F48" t="n">
+        <v>329710</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B49" t="n">
+        <v>66.02999877929688</v>
+      </c>
+      <c r="C49" t="n">
+        <v>67.59999847412109</v>
+      </c>
+      <c r="D49" t="n">
+        <v>65.80000305175781</v>
+      </c>
+      <c r="E49" t="n">
+        <v>67.11000061035156</v>
+      </c>
+      <c r="F49" t="n">
+        <v>249633</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B50" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="C50" t="n">
+        <v>67.16999816894531</v>
+      </c>
+      <c r="D50" t="n">
+        <v>65.29000091552734</v>
+      </c>
+      <c r="E50" t="n">
+        <v>65.94999694824219</v>
+      </c>
+      <c r="F50" t="n">
+        <v>222511</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B51" t="n">
+        <v>67.68000030517578</v>
+      </c>
+      <c r="C51" t="n">
+        <v>67.87999725341797</v>
+      </c>
+      <c r="D51" t="n">
+        <v>66.15000152587891</v>
+      </c>
+      <c r="E51" t="n">
+        <v>66.62000274658203</v>
+      </c>
+      <c r="F51" t="n">
+        <v>246675</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B52" t="n">
+        <v>66.55000305175781</v>
+      </c>
+      <c r="C52" t="n">
+        <v>67.94000244140625</v>
+      </c>
+      <c r="D52" t="n">
+        <v>66.37000274658203</v>
+      </c>
+      <c r="E52" t="n">
+        <v>67.69000244140625</v>
+      </c>
+      <c r="F52" t="n">
+        <v>268590</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45730</v>
+      </c>
+      <c r="B53" t="n">
+        <v>67.18000030517578</v>
+      </c>
+      <c r="C53" t="n">
+        <v>67.48000335693359</v>
+      </c>
+      <c r="D53" t="n">
+        <v>66.58999633789062</v>
+      </c>
+      <c r="E53" t="n">
+        <v>66.77999877929688</v>
+      </c>
+      <c r="F53" t="n">
+        <v>180495</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B54" t="n">
+        <v>67.58000183105469</v>
+      </c>
+      <c r="C54" t="n">
+        <v>68.37000274658203</v>
+      </c>
+      <c r="D54" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="E54" t="n">
+        <v>67.34999847412109</v>
+      </c>
+      <c r="F54" t="n">
+        <v>161298</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45734</v>
+      </c>
+      <c r="B55" t="n">
+        <v>66.90000152587891</v>
+      </c>
+      <c r="C55" t="n">
+        <v>68.72000122070312</v>
+      </c>
+      <c r="D55" t="n">
+        <v>66.55999755859375</v>
+      </c>
+      <c r="E55" t="n">
+        <v>67.40000152587891</v>
+      </c>
+      <c r="F55" t="n">
+        <v>110338</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45735</v>
+      </c>
+      <c r="B56" t="n">
+        <v>67.16000366210938</v>
+      </c>
+      <c r="C56" t="n">
+        <v>67.62999725341797</v>
+      </c>
+      <c r="D56" t="n">
+        <v>66.20999908447266</v>
+      </c>
+      <c r="E56" t="n">
+        <v>66.72000122070312</v>
+      </c>
+      <c r="F56" t="n">
+        <v>73077</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="B57" t="n">
+        <v>68.26000213623047</v>
+      </c>
+      <c r="C57" t="n">
+        <v>68.47000122070312</v>
+      </c>
+      <c r="D57" t="n">
+        <v>66.87999725341797</v>
+      </c>
+      <c r="E57" t="n">
+        <v>67.29000091552734</v>
+      </c>
+      <c r="F57" t="n">
+        <v>283376</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45737</v>
+      </c>
+      <c r="B58" t="n">
+        <v>68.27999877929688</v>
+      </c>
+      <c r="C58" t="n">
+        <v>68.65000152587891</v>
+      </c>
+      <c r="D58" t="n">
+        <v>67.65000152587891</v>
+      </c>
+      <c r="E58" t="n">
+        <v>68.34999847412109</v>
+      </c>
+      <c r="F58" t="n">
+        <v>198964</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45740</v>
+      </c>
+      <c r="B59" t="n">
+        <v>69.11000061035156</v>
+      </c>
+      <c r="C59" t="n">
+        <v>69.33000183105469</v>
+      </c>
+      <c r="D59" t="n">
+        <v>67.94999694824219</v>
+      </c>
+      <c r="E59" t="n">
+        <v>68.34999847412109</v>
+      </c>
+      <c r="F59" t="n">
+        <v>247024</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45741</v>
+      </c>
+      <c r="B60" t="n">
+        <v>69</v>
+      </c>
+      <c r="C60" t="n">
+        <v>69.68000030517578</v>
+      </c>
+      <c r="D60" t="n">
+        <v>68.51999664306641</v>
+      </c>
+      <c r="E60" t="n">
+        <v>69.16000366210938</v>
+      </c>
+      <c r="F60" t="n">
+        <v>258411</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45742</v>
+      </c>
+      <c r="B61" t="n">
+        <v>69.65000152587891</v>
+      </c>
+      <c r="C61" t="n">
+        <v>70.22000122070312</v>
+      </c>
+      <c r="D61" t="n">
+        <v>69.05999755859375</v>
+      </c>
+      <c r="E61" t="n">
+        <v>69.16000366210938</v>
+      </c>
+      <c r="F61" t="n">
+        <v>262413</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45743</v>
+      </c>
+      <c r="B62" t="n">
+        <v>69.91999816894531</v>
+      </c>
+      <c r="C62" t="n">
+        <v>69.97000122070312</v>
+      </c>
+      <c r="D62" t="n">
+        <v>69.12000274658203</v>
+      </c>
+      <c r="E62" t="n">
+        <v>69.95999908447266</v>
+      </c>
+      <c r="F62" t="n">
+        <v>211825</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45744</v>
+      </c>
+      <c r="B63" t="n">
+        <v>69.36000061035156</v>
+      </c>
+      <c r="C63" t="n">
+        <v>70.08999633789062</v>
+      </c>
+      <c r="D63" t="n">
+        <v>68.87000274658203</v>
+      </c>
+      <c r="E63" t="n">
+        <v>69.91000366210938</v>
+      </c>
+      <c r="F63" t="n">
+        <v>246650</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B64" t="n">
+        <v>71.48000335693359</v>
+      </c>
+      <c r="C64" t="n">
+        <v>71.83000183105469</v>
+      </c>
+      <c r="D64" t="n">
+        <v>68.80999755859375</v>
+      </c>
+      <c r="E64" t="n">
+        <v>69.43000030517578</v>
+      </c>
+      <c r="F64" t="n">
+        <v>313087</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B65" t="n">
+        <v>71.19999694824219</v>
+      </c>
+      <c r="C65" t="n">
+        <v>72.09999847412109</v>
+      </c>
+      <c r="D65" t="n">
+        <v>71.02999877929688</v>
+      </c>
+      <c r="E65" t="n">
+        <v>71.38999938964844</v>
+      </c>
+      <c r="F65" t="n">
+        <v>272832</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45749</v>
+      </c>
+      <c r="B66" t="n">
+        <v>71.70999908447266</v>
+      </c>
+      <c r="C66" t="n">
+        <v>72.27999877929688</v>
+      </c>
+      <c r="D66" t="n">
+        <v>70.58999633789062</v>
+      </c>
+      <c r="E66" t="n">
+        <v>71.19999694824219</v>
+      </c>
+      <c r="F66" t="n">
+        <v>286501</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45750</v>
+      </c>
+      <c r="B67" t="n">
+        <v>66.94999694824219</v>
+      </c>
+      <c r="C67" t="n">
+        <v>70.41000366210938</v>
+      </c>
+      <c r="D67" t="n">
+        <v>65.98000335693359</v>
+      </c>
+      <c r="E67" t="n">
+        <v>70.37999725341797</v>
+      </c>
+      <c r="F67" t="n">
+        <v>459238</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45751</v>
+      </c>
+      <c r="B68" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="C68" t="n">
+        <v>66.90000152587891</v>
+      </c>
+      <c r="D68" t="n">
+        <v>60.45000076293945</v>
+      </c>
+      <c r="E68" t="n">
+        <v>66.63999938964844</v>
+      </c>
+      <c r="F68" t="n">
+        <v>559638</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45754</v>
+      </c>
+      <c r="B69" t="n">
+        <v>60.70000076293945</v>
+      </c>
+      <c r="C69" t="n">
+        <v>63.90000152587891</v>
+      </c>
+      <c r="D69" t="n">
+        <v>58.95000076293945</v>
+      </c>
+      <c r="E69" t="n">
+        <v>61.11999893188477</v>
+      </c>
+      <c r="F69" t="n">
+        <v>597617</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="B70" t="n">
+        <v>59.58000183105469</v>
+      </c>
+      <c r="C70" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="D70" t="n">
+        <v>57.88000106811523</v>
+      </c>
+      <c r="E70" t="n">
+        <v>61.02999877929688</v>
+      </c>
+      <c r="F70" t="n">
+        <v>557655</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>45756</v>
+      </c>
+      <c r="B71" t="n">
+        <v>62.34999847412109</v>
+      </c>
+      <c r="C71" t="n">
+        <v>62.93000030517578</v>
+      </c>
+      <c r="D71" t="n">
+        <v>55.11999893188477</v>
+      </c>
+      <c r="E71" t="n">
+        <v>58.31999969482422</v>
+      </c>
+      <c r="F71" t="n">
+        <v>592250</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45757</v>
+      </c>
+      <c r="B72" t="n">
+        <v>60.06999969482422</v>
+      </c>
+      <c r="C72" t="n">
+        <v>63.34000015258789</v>
+      </c>
+      <c r="D72" t="n">
+        <v>58.7599983215332</v>
+      </c>
+      <c r="E72" t="n">
+        <v>62.70999908447266</v>
+      </c>
+      <c r="F72" t="n">
+        <v>391826</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>45758</v>
+      </c>
+      <c r="B73" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C73" t="n">
+        <v>61.86999893188477</v>
+      </c>
+      <c r="D73" t="n">
+        <v>59.43000030517578</v>
+      </c>
+      <c r="E73" t="n">
+        <v>60.20000076293945</v>
+      </c>
+      <c r="F73" t="n">
+        <v>306231</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B74" t="n">
+        <v>61.52999877929688</v>
+      </c>
+      <c r="C74" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="D74" t="n">
+        <v>60.59000015258789</v>
+      </c>
+      <c r="E74" t="n">
+        <v>61.70000076293945</v>
+      </c>
+      <c r="F74" t="n">
+        <v>238068</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B75" t="n">
+        <v>61.33000183105469</v>
+      </c>
+      <c r="C75" t="n">
+        <v>62.06000137329102</v>
+      </c>
+      <c r="D75" t="n">
+        <v>60.88000106811523</v>
+      </c>
+      <c r="E75" t="n">
+        <v>61.58000183105469</v>
+      </c>
+      <c r="F75" t="n">
+        <v>197404</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>45763</v>
+      </c>
+      <c r="B76" t="n">
+        <v>62.47000122070312</v>
+      </c>
+      <c r="C76" t="n">
+        <v>62.97999954223633</v>
+      </c>
+      <c r="D76" t="n">
+        <v>60.43999862670898</v>
+      </c>
+      <c r="E76" t="n">
+        <v>61.54000091552734</v>
+      </c>
+      <c r="F76" t="n">
+        <v>213194</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B77" t="n">
+        <v>64.68000030517578</v>
+      </c>
+      <c r="C77" t="n">
+        <v>64.86000061035156</v>
+      </c>
+      <c r="D77" t="n">
+        <v>62.61000061035156</v>
+      </c>
+      <c r="E77" t="n">
+        <v>62.63000106811523</v>
+      </c>
+      <c r="F77" t="n">
+        <v>111479</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>45768</v>
+      </c>
+      <c r="B78" t="n">
+        <v>63.08000183105469</v>
+      </c>
+      <c r="C78" t="n">
+        <v>64.41999816894531</v>
+      </c>
+      <c r="D78" t="n">
+        <v>62.45000076293945</v>
+      </c>
+      <c r="E78" t="n">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="F78" t="n">
+        <v>82671</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>45769</v>
+      </c>
+      <c r="B79" t="n">
+        <v>64.30999755859375</v>
+      </c>
+      <c r="C79" t="n">
+        <v>65.08999633789062</v>
+      </c>
+      <c r="D79" t="n">
+        <v>63.43000030517578</v>
+      </c>
+      <c r="E79" t="n">
+        <v>63.43000030517578</v>
+      </c>
+      <c r="F79" t="n">
+        <v>297928</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>45770</v>
+      </c>
+      <c r="B80" t="n">
+        <v>62.27000045776367</v>
+      </c>
+      <c r="C80" t="n">
+        <v>64.87000274658203</v>
+      </c>
+      <c r="D80" t="n">
+        <v>61.52999877929688</v>
+      </c>
+      <c r="E80" t="n">
+        <v>64</v>
+      </c>
+      <c r="F80" t="n">
+        <v>397841</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>45771</v>
+      </c>
+      <c r="B81" t="n">
+        <v>62.79000091552734</v>
+      </c>
+      <c r="C81" t="n">
+        <v>63.31000137329102</v>
+      </c>
+      <c r="D81" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="E81" t="n">
+        <v>62.34000015258789</v>
+      </c>
+      <c r="F81" t="n">
+        <v>264908</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>45772</v>
+      </c>
+      <c r="B82" t="n">
+        <v>63.02000045776367</v>
+      </c>
+      <c r="C82" t="n">
+        <v>63.40999984741211</v>
+      </c>
+      <c r="D82" t="n">
+        <v>61.79999923706055</v>
+      </c>
+      <c r="E82" t="n">
+        <v>62.86000061035156</v>
+      </c>
+      <c r="F82" t="n">
+        <v>283758</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="B83" t="n">
+        <v>62.04999923706055</v>
+      </c>
+      <c r="C83" t="n">
+        <v>63.91999816894531</v>
+      </c>
+      <c r="D83" t="n">
+        <v>61.47999954223633</v>
+      </c>
+      <c r="E83" t="n">
+        <v>63.4900016784668</v>
+      </c>
+      <c r="F83" t="n">
+        <v>276116</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45776</v>
+      </c>
+      <c r="B84" t="n">
+        <v>60.41999816894531</v>
+      </c>
+      <c r="C84" t="n">
+        <v>62.06999969482422</v>
+      </c>
+      <c r="D84" t="n">
+        <v>60.11999893188477</v>
+      </c>
+      <c r="E84" t="n">
+        <v>61.86999893188477</v>
+      </c>
+      <c r="F84" t="n">
+        <v>312373</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58.20999908447266</v>
+      </c>
+      <c r="C85" t="n">
+        <v>60.43000030517578</v>
+      </c>
+      <c r="D85" t="n">
+        <v>57.90999984741211</v>
+      </c>
+      <c r="E85" t="n">
+        <v>60.15999984741211</v>
+      </c>
+      <c r="F85" t="n">
+        <v>419549</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B86" t="n">
+        <v>59.2400016784668</v>
+      </c>
+      <c r="C86" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>56.38999938964844</v>
+      </c>
+      <c r="E86" t="n">
+        <v>58.15999984741211</v>
+      </c>
+      <c r="F86" t="n">
+        <v>364216</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45779</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58.29000091552734</v>
+      </c>
+      <c r="C87" t="n">
+        <v>59.86999893188477</v>
+      </c>
+      <c r="D87" t="n">
+        <v>57.7400016784668</v>
+      </c>
+      <c r="E87" t="n">
+        <v>58.9900016784668</v>
+      </c>
+      <c r="F87" t="n">
+        <v>322096</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45782</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57.13000106811523</v>
+      </c>
+      <c r="C88" t="n">
+        <v>57.70000076293945</v>
+      </c>
+      <c r="D88" t="n">
+        <v>55.29999923706055</v>
+      </c>
+      <c r="E88" t="n">
+        <v>56.7599983215332</v>
+      </c>
+      <c r="F88" t="n">
+        <v>308387</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45783</v>
+      </c>
+      <c r="B89" t="n">
+        <v>59.09000015258789</v>
+      </c>
+      <c r="C89" t="n">
+        <v>59.84000015258789</v>
+      </c>
+      <c r="D89" t="n">
+        <v>57.02999877929688</v>
+      </c>
+      <c r="E89" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="F89" t="n">
+        <v>343893</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45784</v>
+      </c>
+      <c r="B90" t="n">
+        <v>58.06999969482422</v>
+      </c>
+      <c r="C90" t="n">
+        <v>60.2599983215332</v>
+      </c>
+      <c r="D90" t="n">
+        <v>57.81000137329102</v>
+      </c>
+      <c r="E90" t="n">
+        <v>58.97999954223633</v>
+      </c>
+      <c r="F90" t="n">
+        <v>295238</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45785</v>
+      </c>
+      <c r="B91" t="n">
+        <v>59.90999984741211</v>
+      </c>
+      <c r="C91" t="n">
+        <v>60.29000091552734</v>
+      </c>
+      <c r="D91" t="n">
+        <v>57.7400016784668</v>
+      </c>
+      <c r="E91" t="n">
+        <v>57.93000030517578</v>
+      </c>
+      <c r="F91" t="n">
+        <v>281000</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="B92" t="n">
+        <v>61.02000045776367</v>
+      </c>
+      <c r="C92" t="n">
+        <v>61.45000076293945</v>
+      </c>
+      <c r="D92" t="n">
+        <v>59.88999938964844</v>
+      </c>
+      <c r="E92" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="F92" t="n">
+        <v>239640</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="B93" t="n">
+        <v>61.95000076293945</v>
+      </c>
+      <c r="C93" t="n">
+        <v>63.61000061035156</v>
+      </c>
+      <c r="D93" t="n">
+        <v>61.02000045776367</v>
+      </c>
+      <c r="E93" t="n">
+        <v>61.38999938964844</v>
+      </c>
+      <c r="F93" t="n">
+        <v>325865</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45790</v>
+      </c>
+      <c r="B94" t="n">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="C94" t="n">
+        <v>63.90000152587891</v>
+      </c>
+      <c r="D94" t="n">
+        <v>61.65000152587891</v>
+      </c>
+      <c r="E94" t="n">
+        <v>62</v>
+      </c>
+      <c r="F94" t="n">
+        <v>258795</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45791</v>
+      </c>
+      <c r="B95" t="n">
+        <v>63.15000152587891</v>
+      </c>
+      <c r="C95" t="n">
+        <v>63.68000030517578</v>
+      </c>
+      <c r="D95" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="E95" t="n">
+        <v>63.61999893188477</v>
+      </c>
+      <c r="F95" t="n">
+        <v>225626</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45792</v>
+      </c>
+      <c r="B96" t="n">
+        <v>61.61999893188477</v>
+      </c>
+      <c r="C96" t="n">
+        <v>62.90999984741211</v>
+      </c>
+      <c r="D96" t="n">
+        <v>60.47000122070312</v>
+      </c>
+      <c r="E96" t="n">
+        <v>62.88000106811523</v>
+      </c>
+      <c r="F96" t="n">
+        <v>258404</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45793</v>
+      </c>
+      <c r="B97" t="n">
+        <v>62.4900016784668</v>
+      </c>
+      <c r="C97" t="n">
+        <v>62.70999908447266</v>
+      </c>
+      <c r="D97" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="E97" t="n">
+        <v>61.70000076293945</v>
+      </c>
+      <c r="F97" t="n">
+        <v>121556</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="B98" t="n">
+        <v>62.68999862670898</v>
+      </c>
+      <c r="C98" t="n">
+        <v>63.40000152587891</v>
+      </c>
+      <c r="D98" t="n">
+        <v>61.56999969482422</v>
+      </c>
+      <c r="E98" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="F98" t="n">
+        <v>95570</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45797</v>
+      </c>
+      <c r="B99" t="n">
+        <v>62.56000137329102</v>
+      </c>
+      <c r="C99" t="n">
+        <v>63.16999816894531</v>
+      </c>
+      <c r="D99" t="n">
+        <v>62.18999862670898</v>
+      </c>
+      <c r="E99" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="F99" t="n">
+        <v>250414</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45798</v>
+      </c>
+      <c r="B100" t="n">
+        <v>61.56999969482422</v>
+      </c>
+      <c r="C100" t="n">
+        <v>64.19000244140625</v>
+      </c>
+      <c r="D100" t="n">
+        <v>61.27999877929688</v>
+      </c>
+      <c r="E100" t="n">
+        <v>62.27000045776367</v>
+      </c>
+      <c r="F100" t="n">
+        <v>302702</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45799</v>
+      </c>
+      <c r="B101" t="n">
+        <v>61.20000076293945</v>
+      </c>
+      <c r="C101" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="D101" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="E101" t="n">
+        <v>61.33000183105469</v>
+      </c>
+      <c r="F101" t="n">
+        <v>258549</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="B102" t="n">
+        <v>61.52999877929688</v>
+      </c>
+      <c r="C102" t="n">
+        <v>61.88000106811523</v>
+      </c>
+      <c r="D102" t="n">
+        <v>60.02000045776367</v>
+      </c>
+      <c r="E102" t="n">
+        <v>60.81000137329102</v>
+      </c>
+      <c r="F102" t="n">
+        <v>273392</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45804</v>
+      </c>
+      <c r="B103" t="n">
+        <v>60.88999938964844</v>
+      </c>
+      <c r="C103" t="n">
+        <v>62.13999938964844</v>
+      </c>
+      <c r="D103" t="n">
+        <v>60.2599983215332</v>
+      </c>
+      <c r="E103" t="n">
+        <v>61.70000076293945</v>
+      </c>
+      <c r="F103" t="n">
+        <v>291317</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45805</v>
+      </c>
+      <c r="B104" t="n">
+        <v>61.84000015258789</v>
+      </c>
+      <c r="C104" t="n">
+        <v>62.54000091552734</v>
+      </c>
+      <c r="D104" t="n">
+        <v>60.84999847412109</v>
+      </c>
+      <c r="E104" t="n">
+        <v>61.04000091552734</v>
+      </c>
+      <c r="F104" t="n">
+        <v>260374</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45806</v>
+      </c>
+      <c r="B105" t="n">
+        <v>60.93999862670898</v>
+      </c>
+      <c r="C105" t="n">
+        <v>63.06999969482422</v>
+      </c>
+      <c r="D105" t="n">
+        <v>60.54999923706055</v>
+      </c>
+      <c r="E105" t="n">
+        <v>61.83000183105469</v>
+      </c>
+      <c r="F105" t="n">
+        <v>299859</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45807</v>
+      </c>
+      <c r="B106" t="n">
+        <v>60.79000091552734</v>
+      </c>
+      <c r="C106" t="n">
+        <v>61.72000122070312</v>
+      </c>
+      <c r="D106" t="n">
+        <v>59.7400016784668</v>
+      </c>
+      <c r="E106" t="n">
+        <v>60.93999862670898</v>
+      </c>
+      <c r="F106" t="n">
+        <v>384927</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B107" t="n">
+        <v>62.52000045776367</v>
+      </c>
+      <c r="C107" t="n">
+        <v>63.88000106811523</v>
+      </c>
+      <c r="D107" t="n">
+        <v>61.06000137329102</v>
+      </c>
+      <c r="E107" t="n">
+        <v>61.11000061035156</v>
+      </c>
+      <c r="F107" t="n">
+        <v>403580</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45811</v>
+      </c>
+      <c r="B108" t="n">
+        <v>63.40999984741211</v>
+      </c>
+      <c r="C108" t="n">
+        <v>63.88999938964844</v>
+      </c>
+      <c r="D108" t="n">
+        <v>62.40000152587891</v>
+      </c>
+      <c r="E108" t="n">
+        <v>63.02000045776367</v>
+      </c>
+      <c r="F108" t="n">
+        <v>291260</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45812</v>
+      </c>
+      <c r="B109" t="n">
+        <v>62.84999847412109</v>
+      </c>
+      <c r="C109" t="n">
+        <v>63.95999908447266</v>
+      </c>
+      <c r="D109" t="n">
+        <v>62.16999816894531</v>
+      </c>
+      <c r="E109" t="n">
+        <v>63.36000061035156</v>
+      </c>
+      <c r="F109" t="n">
+        <v>321128</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45813</v>
+      </c>
+      <c r="B110" t="n">
+        <v>63.36999893188477</v>
+      </c>
+      <c r="C110" t="n">
+        <v>63.97999954223633</v>
+      </c>
+      <c r="D110" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>62.7599983215332</v>
+      </c>
+      <c r="F110" t="n">
+        <v>232423</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45814</v>
+      </c>
+      <c r="B111" t="n">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="C111" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="D111" t="n">
+        <v>62.81999969482422</v>
+      </c>
+      <c r="E111" t="n">
+        <v>63.33000183105469</v>
+      </c>
+      <c r="F111" t="n">
+        <v>310133</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B112" t="n">
+        <v>65.29000091552734</v>
+      </c>
+      <c r="C112" t="n">
+        <v>65.43000030517578</v>
+      </c>
+      <c r="D112" t="n">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="E112" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="F112" t="n">
+        <v>235900</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45818</v>
+      </c>
+      <c r="B113" t="n">
+        <v>64.98000335693359</v>
+      </c>
+      <c r="C113" t="n">
+        <v>66.27999877929688</v>
+      </c>
+      <c r="D113" t="n">
+        <v>64.56999969482422</v>
+      </c>
+      <c r="E113" t="n">
+        <v>65.45999908447266</v>
+      </c>
+      <c r="F113" t="n">
+        <v>279021</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45819</v>
+      </c>
+      <c r="B114" t="n">
+        <v>68.15000152587891</v>
+      </c>
+      <c r="C114" t="n">
+        <v>68.37000274658203</v>
+      </c>
+      <c r="D114" t="n">
+        <v>64.59999847412109</v>
+      </c>
+      <c r="E114" t="n">
+        <v>64.76000213623047</v>
+      </c>
+      <c r="F114" t="n">
+        <v>378473</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45820</v>
+      </c>
+      <c r="B115" t="n">
+        <v>68.04000091552734</v>
+      </c>
+      <c r="C115" t="n">
+        <v>69.29000091552734</v>
+      </c>
+      <c r="D115" t="n">
+        <v>66.72000122070312</v>
+      </c>
+      <c r="E115" t="n">
+        <v>69.02999877929688</v>
+      </c>
+      <c r="F115" t="n">
+        <v>379394</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45821</v>
+      </c>
+      <c r="B116" t="n">
+        <v>72.98000335693359</v>
+      </c>
+      <c r="C116" t="n">
+        <v>77.62000274658203</v>
+      </c>
+      <c r="D116" t="n">
+        <v>68.48999786376953</v>
+      </c>
+      <c r="E116" t="n">
+        <v>68.90000152587891</v>
+      </c>
+      <c r="F116" t="n">
+        <v>715652</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45824</v>
+      </c>
+      <c r="B117" t="n">
+        <v>71.76999664306641</v>
+      </c>
+      <c r="C117" t="n">
+        <v>77.48999786376953</v>
+      </c>
+      <c r="D117" t="n">
+        <v>69.37999725341797</v>
+      </c>
+      <c r="E117" t="n">
+        <v>76.54000091552734</v>
+      </c>
+      <c r="F117" t="n">
+        <v>367312</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45825</v>
+      </c>
+      <c r="B118" t="n">
+        <v>74.83999633789062</v>
+      </c>
+      <c r="C118" t="n">
+        <v>75.54000091552734</v>
+      </c>
+      <c r="D118" t="n">
+        <v>71</v>
+      </c>
+      <c r="E118" t="n">
+        <v>71.11000061035156</v>
+      </c>
+      <c r="F118" t="n">
+        <v>154264</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B119" t="n">
+        <v>75.13999938964844</v>
+      </c>
+      <c r="C119" t="n">
+        <v>76.06999969482422</v>
+      </c>
+      <c r="D119" t="n">
+        <v>72.94000244140625</v>
+      </c>
+      <c r="E119" t="n">
+        <v>75.61000061035156</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45828</v>
+      </c>
+      <c r="B120" t="n">
+        <v>74.93000030517578</v>
+      </c>
+      <c r="C120" t="n">
+        <v>77.58000183105469</v>
+      </c>
+      <c r="D120" t="n">
+        <v>74.30000305175781</v>
+      </c>
+      <c r="E120" t="n">
+        <v>74.59999847412109</v>
+      </c>
+      <c r="F120" t="n">
+        <v>678377</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45831</v>
+      </c>
+      <c r="B121" t="n">
+        <v>68.51000213623047</v>
+      </c>
+      <c r="C121" t="n">
+        <v>78.40000152587891</v>
+      </c>
+      <c r="D121" t="n">
+        <v>66.59999847412109</v>
+      </c>
+      <c r="E121" t="n">
+        <v>78</v>
+      </c>
+      <c r="F121" t="n">
+        <v>728868</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45832</v>
+      </c>
+      <c r="B122" t="n">
+        <v>64.37000274658203</v>
+      </c>
+      <c r="C122" t="n">
+        <v>67.83000183105469</v>
+      </c>
+      <c r="D122" t="n">
+        <v>64</v>
+      </c>
+      <c r="E122" t="n">
+        <v>67.73999786376953</v>
+      </c>
+      <c r="F122" t="n">
+        <v>541475</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="B123" t="n">
+        <v>64.91999816894531</v>
+      </c>
+      <c r="C123" t="n">
+        <v>66.02999877929688</v>
+      </c>
+      <c r="D123" t="n">
+        <v>64.51000213623047</v>
+      </c>
+      <c r="E123" t="n">
+        <v>65.12000274658203</v>
+      </c>
+      <c r="F123" t="n">
+        <v>278504</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45834</v>
+      </c>
+      <c r="B124" t="n">
+        <v>65.23999786376953</v>
+      </c>
+      <c r="C124" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="D124" t="n">
+        <v>64.66000366210938</v>
+      </c>
+      <c r="E124" t="n">
+        <v>64.98000335693359</v>
+      </c>
+      <c r="F124" t="n">
+        <v>233771</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="B125" t="n">
+        <v>65.51999664306641</v>
+      </c>
+      <c r="C125" t="n">
+        <v>66.08999633789062</v>
+      </c>
+      <c r="D125" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="E125" t="n">
+        <v>65.30000305175781</v>
+      </c>
+      <c r="F125" t="n">
+        <v>236284</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B126" t="n">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="C126" t="n">
+        <v>65.81999969482422</v>
+      </c>
+      <c r="D126" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E126" t="n">
+        <v>65.15000152587891</v>
+      </c>
+      <c r="F126" t="n">
+        <v>193289</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B127" t="n">
+        <v>65.44999694824219</v>
+      </c>
+      <c r="C127" t="n">
+        <v>65.98000335693359</v>
+      </c>
+      <c r="D127" t="n">
+        <v>64.66999816894531</v>
+      </c>
+      <c r="E127" t="n">
+        <v>64.95999908447266</v>
+      </c>
+      <c r="F127" t="n">
+        <v>193162</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="B128" t="n">
+        <v>67.44999694824219</v>
+      </c>
+      <c r="C128" t="n">
+        <v>67.58000183105469</v>
+      </c>
+      <c r="D128" t="n">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="E128" t="n">
+        <v>65.55999755859375</v>
+      </c>
+      <c r="F128" t="n">
+        <v>265200</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="B129" t="n">
+        <v>67</v>
+      </c>
+      <c r="C129" t="n">
+        <v>67.58000183105469</v>
+      </c>
+      <c r="D129" t="n">
+        <v>66.52999877929688</v>
+      </c>
+      <c r="E129" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45842</v>
+      </c>
+      <c r="B130" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="C130" t="n">
+        <v>67.18000030517578</v>
+      </c>
+      <c r="D130" t="n">
+        <v>66.04000091552734</v>
+      </c>
+      <c r="E130" t="n">
+        <v>67.12999725341797</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45845</v>
+      </c>
+      <c r="B131" t="n">
+        <v>67.93000030517578</v>
+      </c>
+      <c r="C131" t="n">
+        <v>68.31999969482422</v>
+      </c>
+      <c r="D131" t="n">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="E131" t="n">
+        <v>65.69999694824219</v>
+      </c>
+      <c r="F131" t="n">
+        <v>332949</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45846</v>
+      </c>
+      <c r="B132" t="n">
+        <v>68.33000183105469</v>
+      </c>
+      <c r="C132" t="n">
+        <v>68.91000366210938</v>
+      </c>
+      <c r="D132" t="n">
+        <v>67.33000183105469</v>
+      </c>
+      <c r="E132" t="n">
+        <v>67.95999908447266</v>
+      </c>
+      <c r="F132" t="n">
+        <v>219882</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="B133" t="n">
+        <v>68.37999725341797</v>
+      </c>
+      <c r="C133" t="n">
+        <v>68.94000244140625</v>
+      </c>
+      <c r="D133" t="n">
+        <v>67.69999694824219</v>
+      </c>
+      <c r="E133" t="n">
+        <v>68.18000030517578</v>
+      </c>
+      <c r="F133" t="n">
+        <v>223945</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B134" t="n">
+        <v>66.56999969482422</v>
+      </c>
+      <c r="C134" t="n">
+        <v>68.65000152587891</v>
+      </c>
+      <c r="D134" t="n">
+        <v>66.44999694824219</v>
+      </c>
+      <c r="E134" t="n">
+        <v>68.29000091552734</v>
+      </c>
+      <c r="F134" t="n">
+        <v>258654</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B135" t="n">
+        <v>68.44999694824219</v>
+      </c>
+      <c r="C135" t="n">
+        <v>68.76999664306641</v>
+      </c>
+      <c r="D135" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E135" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="F135" t="n">
+        <v>226297</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>45852</v>
+      </c>
+      <c r="B136" t="n">
+        <v>66.98000335693359</v>
+      </c>
+      <c r="C136" t="n">
+        <v>69.65000152587891</v>
+      </c>
+      <c r="D136" t="n">
+        <v>66.80000305175781</v>
+      </c>
+      <c r="E136" t="n">
+        <v>68.68000030517578</v>
+      </c>
+      <c r="F136" t="n">
+        <v>263877</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>45853</v>
+      </c>
+      <c r="B137" t="n">
+        <v>66.51999664306641</v>
+      </c>
+      <c r="C137" t="n">
+        <v>67.12999725341797</v>
+      </c>
+      <c r="D137" t="n">
+        <v>66.22000122070312</v>
+      </c>
+      <c r="E137" t="n">
+        <v>66.86000061035156</v>
+      </c>
+      <c r="F137" t="n">
+        <v>252724</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>45854</v>
+      </c>
+      <c r="B138" t="n">
+        <v>66.37999725341797</v>
+      </c>
+      <c r="C138" t="n">
+        <v>67.01000213623047</v>
+      </c>
+      <c r="D138" t="n">
+        <v>65.41999816894531</v>
+      </c>
+      <c r="E138" t="n">
+        <v>66.73000335693359</v>
+      </c>
+      <c r="F138" t="n">
+        <v>248346</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="B139" t="n">
+        <v>67.54000091552734</v>
+      </c>
+      <c r="C139" t="n">
+        <v>67.69000244140625</v>
+      </c>
+      <c r="D139" t="n">
+        <v>66.29000091552734</v>
+      </c>
+      <c r="E139" t="n">
+        <v>66.59999847412109</v>
+      </c>
+      <c r="F139" t="n">
+        <v>188802</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>45856</v>
+      </c>
+      <c r="B140" t="n">
+        <v>67.33999633789062</v>
+      </c>
+      <c r="C140" t="n">
+        <v>68.95999908447266</v>
+      </c>
+      <c r="D140" t="n">
+        <v>67.19999694824219</v>
+      </c>
+      <c r="E140" t="n">
+        <v>67.59999847412109</v>
+      </c>
+      <c r="F140" t="n">
+        <v>107628</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>45859</v>
+      </c>
+      <c r="B141" t="n">
+        <v>67.19999694824219</v>
+      </c>
+      <c r="C141" t="n">
+        <v>67.76000213623047</v>
+      </c>
+      <c r="D141" t="n">
+        <v>66.45999908447266</v>
+      </c>
+      <c r="E141" t="n">
+        <v>67.31999969482422</v>
+      </c>
+      <c r="F141" t="n">
+        <v>81194</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="B142" t="n">
+        <v>66.20999908447266</v>
+      </c>
+      <c r="C142" t="n">
+        <v>67.12999725341797</v>
+      </c>
+      <c r="D142" t="n">
+        <v>65.98999786376953</v>
+      </c>
+      <c r="E142" t="n">
+        <v>67.12000274658203</v>
+      </c>
+      <c r="F142" t="n">
+        <v>269991</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="B143" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="C143" t="n">
+        <v>65.77999877929688</v>
+      </c>
+      <c r="D143" t="n">
+        <v>64.70999908447266</v>
+      </c>
+      <c r="E143" t="n">
+        <v>65.48999786376953</v>
+      </c>
+      <c r="F143" t="n">
+        <v>251825</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B144" t="n">
+        <v>66.02999877929688</v>
+      </c>
+      <c r="C144" t="n">
+        <v>66.38999938964844</v>
+      </c>
+      <c r="D144" t="n">
+        <v>65.33000183105469</v>
+      </c>
+      <c r="E144" t="n">
+        <v>65.41999816894531</v>
+      </c>
+      <c r="F144" t="n">
+        <v>281209</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="B145" t="n">
+        <v>65.16000366210938</v>
+      </c>
+      <c r="C145" t="n">
+        <v>66.73999786376953</v>
+      </c>
+      <c r="D145" t="n">
+        <v>65</v>
+      </c>
+      <c r="E145" t="n">
+        <v>66.15000152587891</v>
+      </c>
+      <c r="F145" t="n">
+        <v>234283</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45866</v>
+      </c>
+      <c r="B146" t="n">
+        <v>66.70999908447266</v>
+      </c>
+      <c r="C146" t="n">
+        <v>67.13999938964844</v>
+      </c>
+      <c r="D146" t="n">
+        <v>65.05000305175781</v>
+      </c>
+      <c r="E146" t="n">
+        <v>65.15000152587891</v>
+      </c>
+      <c r="F146" t="n">
+        <v>262038</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45867</v>
+      </c>
+      <c r="B147" t="n">
+        <v>69.20999908447266</v>
+      </c>
+      <c r="C147" t="n">
+        <v>69.76000213623047</v>
+      </c>
+      <c r="D147" t="n">
+        <v>66.52999877929688</v>
+      </c>
+      <c r="E147" t="n">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="F147" t="n">
+        <v>329112</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="B148" t="n">
+        <v>70</v>
+      </c>
+      <c r="C148" t="n">
+        <v>70.51000213623047</v>
+      </c>
+      <c r="D148" t="n">
+        <v>68.44999694824219</v>
+      </c>
+      <c r="E148" t="n">
+        <v>69.33999633789062</v>
+      </c>
+      <c r="F148" t="n">
+        <v>345336</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B149" t="n">
+        <v>69.26000213623047</v>
+      </c>
+      <c r="C149" t="n">
+        <v>70.41000366210938</v>
+      </c>
+      <c r="D149" t="n">
+        <v>68.55999755859375</v>
+      </c>
+      <c r="E149" t="n">
+        <v>70.30000305175781</v>
+      </c>
+      <c r="F149" t="n">
+        <v>247031</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B150" t="n">
+        <v>67.33000183105469</v>
+      </c>
+      <c r="C150" t="n">
+        <v>69.58000183105469</v>
+      </c>
+      <c r="D150" t="n">
+        <v>67.05000305175781</v>
+      </c>
+      <c r="E150" t="n">
+        <v>69.34999847412109</v>
+      </c>
+      <c r="F150" t="n">
+        <v>355819</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="B151" t="n">
+        <v>66.29000091552734</v>
+      </c>
+      <c r="C151" t="n">
+        <v>67.73999786376953</v>
+      </c>
+      <c r="D151" t="n">
+        <v>65.45999908447266</v>
+      </c>
+      <c r="E151" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="F151" t="n">
+        <v>277375</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45874</v>
+      </c>
+      <c r="B152" t="n">
+        <v>65.16000366210938</v>
+      </c>
+      <c r="C152" t="n">
+        <v>66.38999938964844</v>
+      </c>
+      <c r="D152" t="n">
+        <v>65.02999877929688</v>
+      </c>
+      <c r="E152" t="n">
+        <v>66.20999908447266</v>
+      </c>
+      <c r="F152" t="n">
+        <v>279030</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45875</v>
+      </c>
+      <c r="B153" t="n">
+        <v>64.34999847412109</v>
+      </c>
+      <c r="C153" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="D153" t="n">
+        <v>63.63999938964844</v>
+      </c>
+      <c r="E153" t="n">
+        <v>65.15000152587891</v>
+      </c>
+      <c r="F153" t="n">
+        <v>353827</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45876</v>
+      </c>
+      <c r="B154" t="n">
+        <v>63.88000106811523</v>
+      </c>
+      <c r="C154" t="n">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="D154" t="n">
+        <v>63.70000076293945</v>
+      </c>
+      <c r="E154" t="n">
+        <v>64.36000061035156</v>
+      </c>
+      <c r="F154" t="n">
+        <v>300518</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45877</v>
+      </c>
+      <c r="B155" t="n">
+        <v>63.88000106811523</v>
+      </c>
+      <c r="C155" t="n">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="D155" t="n">
+        <v>62.77000045776367</v>
+      </c>
+      <c r="E155" t="n">
+        <v>63.84999847412109</v>
+      </c>
+      <c r="F155" t="n">
+        <v>322939</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45880</v>
+      </c>
+      <c r="B156" t="n">
+        <v>63.95999908447266</v>
+      </c>
+      <c r="C156" t="n">
+        <v>64.44000244140625</v>
+      </c>
+      <c r="D156" t="n">
+        <v>63.02000045776367</v>
+      </c>
+      <c r="E156" t="n">
+        <v>63.47999954223633</v>
+      </c>
+      <c r="F156" t="n">
+        <v>234807</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="B157" t="n">
+        <v>63.16999816894531</v>
+      </c>
+      <c r="C157" t="n">
+        <v>64.33999633789062</v>
+      </c>
+      <c r="D157" t="n">
+        <v>63.06000137329102</v>
+      </c>
+      <c r="E157" t="n">
+        <v>64</v>
+      </c>
+      <c r="F157" t="n">
+        <v>304441</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45882</v>
+      </c>
+      <c r="B158" t="n">
+        <v>62.65000152587891</v>
+      </c>
+      <c r="C158" t="n">
+        <v>63.38000106811523</v>
+      </c>
+      <c r="D158" t="n">
+        <v>61.93999862670898</v>
+      </c>
+      <c r="E158" t="n">
+        <v>63.06999969482422</v>
+      </c>
+      <c r="F158" t="n">
+        <v>298939</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45883</v>
+      </c>
+      <c r="B159" t="n">
+        <v>63.95999908447266</v>
+      </c>
+      <c r="C159" t="n">
+        <v>64.09999847412109</v>
+      </c>
+      <c r="D159" t="n">
+        <v>62.58000183105469</v>
+      </c>
+      <c r="E159" t="n">
+        <v>62.79000091552734</v>
+      </c>
+      <c r="F159" t="n">
+        <v>251652</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="B160" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="C160" t="n">
+        <v>64.15000152587891</v>
+      </c>
+      <c r="D160" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="E160" t="n">
+        <v>63.90999984741211</v>
+      </c>
+      <c r="F160" t="n">
+        <v>197390</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B161" t="n">
+        <v>63.41999816894531</v>
+      </c>
+      <c r="C161" t="n">
+        <v>63.79000091552734</v>
+      </c>
+      <c r="D161" t="n">
+        <v>62.18000030517578</v>
+      </c>
+      <c r="E161" t="n">
+        <v>63</v>
+      </c>
+      <c r="F161" t="n">
+        <v>95113</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="B162" t="n">
+        <v>62.34999847412109</v>
+      </c>
+      <c r="C162" t="n">
+        <v>63.38999938964844</v>
+      </c>
+      <c r="D162" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="E162" t="n">
+        <v>63.27000045776367</v>
+      </c>
+      <c r="F162" t="n">
+        <v>99484</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="B163" t="n">
+        <v>63.20999908447266</v>
+      </c>
+      <c r="C163" t="n">
+        <v>63.54999923706055</v>
+      </c>
+      <c r="D163" t="n">
+        <v>62.38999938964844</v>
+      </c>
+      <c r="E163" t="n">
+        <v>62.59999847412109</v>
+      </c>
+      <c r="F163" t="n">
+        <v>280663</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="B164" t="n">
+        <v>63.52000045776367</v>
+      </c>
+      <c r="C164" t="n">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="D164" t="n">
+        <v>62.52000045776367</v>
+      </c>
+      <c r="E164" t="n">
+        <v>62.84999847412109</v>
+      </c>
+      <c r="F164" t="n">
+        <v>250166</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="B165" t="n">
+        <v>63.65999984741211</v>
+      </c>
+      <c r="C165" t="n">
+        <v>63.93000030517578</v>
+      </c>
+      <c r="D165" t="n">
+        <v>63.31000137329102</v>
+      </c>
+      <c r="E165" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F165" t="n">
+        <v>223169</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B166" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="C166" t="n">
+        <v>65.09999847412109</v>
+      </c>
+      <c r="D166" t="n">
+        <v>63.52999877929688</v>
+      </c>
+      <c r="E166" t="n">
+        <v>63.88000106811523</v>
+      </c>
+      <c r="F166" t="n">
+        <v>185270</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B167" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="C167" t="n">
+        <v>64.76000213623047</v>
+      </c>
+      <c r="D167" t="n">
+        <v>63.13000106811523</v>
+      </c>
+      <c r="E167" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="F167" t="n">
+        <v>199101</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B168" t="n">
+        <v>64.15000152587891</v>
+      </c>
+      <c r="C168" t="n">
+        <v>64.23000335693359</v>
+      </c>
+      <c r="D168" t="n">
+        <v>62.95000076293945</v>
+      </c>
+      <c r="E168" t="n">
+        <v>63.31000137329102</v>
+      </c>
+      <c r="F168" t="n">
+        <v>193476</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B169" t="n">
+        <v>64.59999847412109</v>
+      </c>
+      <c r="C169" t="n">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="D169" t="n">
+        <v>63.34999847412109</v>
+      </c>
+      <c r="E169" t="n">
+        <v>63.86999893188477</v>
+      </c>
+      <c r="F169" t="n">
+        <v>208931</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B170" t="n">
+        <v>64.01000213623047</v>
+      </c>
+      <c r="C170" t="n">
+        <v>64.55000305175781</v>
+      </c>
+      <c r="D170" t="n">
+        <v>63.88000106811523</v>
+      </c>
+      <c r="E170" t="n">
+        <v>64.26000213623047</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B171" t="n">
+        <v>65.58999633789062</v>
+      </c>
+      <c r="C171" t="n">
+        <v>66.02999877929688</v>
+      </c>
+      <c r="D171" t="n">
+        <v>63.65999984741211</v>
+      </c>
+      <c r="E171" t="n">
+        <v>63.95000076293945</v>
+      </c>
+      <c r="F171" t="n">
+        <v>320218</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B172" t="n">
+        <v>63.97000122070312</v>
+      </c>
+      <c r="C172" t="n">
+        <v>65.72000122070312</v>
+      </c>
+      <c r="D172" t="n">
+        <v>63.72000122070312</v>
+      </c>
+      <c r="E172" t="n">
+        <v>65.62000274658203</v>
+      </c>
+      <c r="F172" t="n">
+        <v>298737</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B173" t="n">
+        <v>63.47999954223633</v>
+      </c>
+      <c r="C173" t="n">
+        <v>63.84000015258789</v>
+      </c>
+      <c r="D173" t="n">
+        <v>62.72000122070312</v>
+      </c>
+      <c r="E173" t="n">
+        <v>63.81999969482422</v>
+      </c>
+      <c r="F173" t="n">
+        <v>251689</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B174" t="n">
+        <v>61.86999893188477</v>
+      </c>
+      <c r="C174" t="n">
+        <v>63.4900016784668</v>
+      </c>
+      <c r="D174" t="n">
+        <v>61.45000076293945</v>
+      </c>
+      <c r="E174" t="n">
+        <v>63.33000183105469</v>
+      </c>
+      <c r="F174" t="n">
+        <v>294540</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B175" t="n">
+        <v>62.2599983215332</v>
+      </c>
+      <c r="C175" t="n">
+        <v>63.34000015258789</v>
+      </c>
+      <c r="D175" t="n">
+        <v>61.84999847412109</v>
+      </c>
+      <c r="E175" t="n">
+        <v>62</v>
+      </c>
+      <c r="F175" t="n">
+        <v>237288</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B176" t="n">
+        <v>62.63000106811523</v>
+      </c>
+      <c r="C176" t="n">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="D176" t="n">
+        <v>62.36999893188477</v>
+      </c>
+      <c r="E176" t="n">
+        <v>62.43000030517578</v>
+      </c>
+      <c r="F176" t="n">
+        <v>268529</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B177" t="n">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="C177" t="n">
+        <v>64.08000183105469</v>
+      </c>
+      <c r="D177" t="n">
+        <v>62.72000122070312</v>
+      </c>
+      <c r="E177" t="n">
+        <v>62.7400016784668</v>
+      </c>
+      <c r="F177" t="n">
+        <v>260684</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B178" t="n">
+        <v>62.36999893188477</v>
+      </c>
+      <c r="C178" t="n">
+        <v>63.79999923706055</v>
+      </c>
+      <c r="D178" t="n">
+        <v>62.20999908447266</v>
+      </c>
+      <c r="E178" t="n">
+        <v>63.79999923706055</v>
+      </c>
+      <c r="F178" t="n">
+        <v>222661</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B179" t="n">
+        <v>62.68999862670898</v>
+      </c>
+      <c r="C179" t="n">
+        <v>63.97999954223633</v>
+      </c>
+      <c r="D179" t="n">
+        <v>61.68999862670898</v>
+      </c>
+      <c r="E179" t="n">
+        <v>62.27000045776367</v>
+      </c>
+      <c r="F179" t="n">
+        <v>313265</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="B180" t="n">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="C180" t="n">
+        <v>63.66999816894531</v>
+      </c>
+      <c r="D180" t="n">
+        <v>62.52000045776367</v>
+      </c>
+      <c r="E180" t="n">
+        <v>62.97000122070312</v>
+      </c>
+      <c r="F180" t="n">
+        <v>205560</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="B181" t="n">
+        <v>64.51999664306641</v>
+      </c>
+      <c r="C181" t="n">
+        <v>64.76000213623047</v>
+      </c>
+      <c r="D181" t="n">
+        <v>62.88999938964844</v>
+      </c>
+      <c r="E181" t="n">
+        <v>63.31000137329102</v>
+      </c>
+      <c r="F181" t="n">
+        <v>234250</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45917</v>
+      </c>
+      <c r="B182" t="n">
+        <v>64.05000305175781</v>
+      </c>
+      <c r="C182" t="n">
+        <v>64.66999816894531</v>
+      </c>
+      <c r="D182" t="n">
+        <v>63.68999862670898</v>
+      </c>
+      <c r="E182" t="n">
+        <v>64.58999633789062</v>
+      </c>
+      <c r="F182" t="n">
+        <v>165427</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45918</v>
+      </c>
+      <c r="B183" t="n">
+        <v>63.56999969482422</v>
+      </c>
+      <c r="C183" t="n">
+        <v>64.55000305175781</v>
+      </c>
+      <c r="D183" t="n">
+        <v>63.33000183105469</v>
+      </c>
+      <c r="E183" t="n">
+        <v>63.9900016784668</v>
+      </c>
+      <c r="F183" t="n">
+        <v>82321</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B184" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="C184" t="n">
+        <v>63.65000152587891</v>
+      </c>
+      <c r="D184" t="n">
+        <v>62.59999847412109</v>
+      </c>
+      <c r="E184" t="n">
+        <v>63.59000015258789</v>
+      </c>
+      <c r="F184" t="n">
+        <v>87165</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B185" t="n">
+        <v>62.63999938964844</v>
+      </c>
+      <c r="C185" t="n">
+        <v>63.18000030517578</v>
+      </c>
+      <c r="D185" t="n">
+        <v>61.97999954223633</v>
+      </c>
+      <c r="E185" t="n">
+        <v>62.7400016784668</v>
+      </c>
+      <c r="F185" t="n">
+        <v>223779</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45923</v>
+      </c>
+      <c r="B186" t="n">
+        <v>63.40999984741211</v>
+      </c>
+      <c r="C186" t="n">
+        <v>63.88999938964844</v>
+      </c>
+      <c r="D186" t="n">
+        <v>61.84999847412109</v>
+      </c>
+      <c r="E186" t="n">
+        <v>62.33000183105469</v>
+      </c>
+      <c r="F186" t="n">
+        <v>265948</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45924</v>
+      </c>
+      <c r="B187" t="n">
+        <v>64.98999786376953</v>
+      </c>
+      <c r="C187" t="n">
+        <v>65.05000305175781</v>
+      </c>
+      <c r="D187" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="E187" t="n">
+        <v>63.63999938964844</v>
+      </c>
+      <c r="F187" t="n">
+        <v>282721</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="B188" t="n">
+        <v>64.98000335693359</v>
+      </c>
+      <c r="C188" t="n">
+        <v>65.33999633789062</v>
+      </c>
+      <c r="D188" t="n">
+        <v>64.05999755859375</v>
+      </c>
+      <c r="E188" t="n">
+        <v>64.80000305175781</v>
+      </c>
+      <c r="F188" t="n">
+        <v>258353</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B189" t="n">
+        <v>65.72000122070312</v>
+      </c>
+      <c r="C189" t="n">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="D189" t="n">
+        <v>64.66000366210938</v>
+      </c>
+      <c r="E189" t="n">
+        <v>65.19999694824219</v>
+      </c>
+      <c r="F189" t="n">
+        <v>284990</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B190" t="n">
+        <v>63.45000076293945</v>
+      </c>
+      <c r="C190" t="n">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="D190" t="n">
+        <v>62.97999954223633</v>
+      </c>
+      <c r="E190" t="n">
+        <v>65.06999969482422</v>
+      </c>
+      <c r="F190" t="n">
+        <v>294292</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B191" t="n">
+        <v>62.36999893188477</v>
+      </c>
+      <c r="C191" t="n">
+        <v>63.2599983215332</v>
+      </c>
+      <c r="D191" t="n">
+        <v>62.02999877929688</v>
+      </c>
+      <c r="E191" t="n">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="F191" t="n">
+        <v>271649</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B192" t="n">
+        <v>61.77999877929688</v>
+      </c>
+      <c r="C192" t="n">
+        <v>62.88999938964844</v>
+      </c>
+      <c r="D192" t="n">
+        <v>61.40000152587891</v>
+      </c>
+      <c r="E192" t="n">
+        <v>62.45999908447266</v>
+      </c>
+      <c r="F192" t="n">
+        <v>274339</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>45932</v>
+      </c>
+      <c r="B193" t="n">
+        <v>60.47999954223633</v>
+      </c>
+      <c r="C193" t="n">
+        <v>62.54000091552734</v>
+      </c>
+      <c r="D193" t="n">
+        <v>60.40000152587891</v>
+      </c>
+      <c r="E193" t="n">
+        <v>61.77999877929688</v>
+      </c>
+      <c r="F193" t="n">
+        <v>290507</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>45933</v>
+      </c>
+      <c r="B194" t="n">
+        <v>60.88000106811523</v>
+      </c>
+      <c r="C194" t="n">
+        <v>61.38000106811523</v>
+      </c>
+      <c r="D194" t="n">
+        <v>60.54999923706055</v>
+      </c>
+      <c r="E194" t="n">
+        <v>60.70000076293945</v>
+      </c>
+      <c r="F194" t="n">
+        <v>240044</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B195" t="n">
+        <v>61.68999862670898</v>
+      </c>
+      <c r="C195" t="n">
+        <v>62.11999893188477</v>
+      </c>
+      <c r="D195" t="n">
+        <v>61.04000091552734</v>
+      </c>
+      <c r="E195" t="n">
+        <v>61.13999938964844</v>
+      </c>
+      <c r="F195" t="n">
+        <v>224682</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B196" t="n">
+        <v>61.72999954223633</v>
+      </c>
+      <c r="C196" t="n">
+        <v>62.11000061035156</v>
+      </c>
+      <c r="D196" t="n">
+        <v>60.72000122070312</v>
+      </c>
+      <c r="E196" t="n">
+        <v>61.72999954223633</v>
+      </c>
+      <c r="F196" t="n">
+        <v>245121</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B197" t="n">
+        <v>62.54999923706055</v>
+      </c>
+      <c r="C197" t="n">
+        <v>62.91999816894531</v>
+      </c>
+      <c r="D197" t="n">
+        <v>62.04999923706055</v>
+      </c>
+      <c r="E197" t="n">
+        <v>62.04999923706055</v>
+      </c>
+      <c r="F197" t="n">
+        <v>273318</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B198" t="n">
+        <v>61.5099983215332</v>
+      </c>
+      <c r="C198" t="n">
+        <v>62.86999893188477</v>
+      </c>
+      <c r="D198" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="E198" t="n">
+        <v>62.31000137329102</v>
+      </c>
+      <c r="F198" t="n">
+        <v>259171</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B199" t="n">
+        <v>58.90000152587891</v>
+      </c>
+      <c r="C199" t="n">
+        <v>61.66999816894531</v>
+      </c>
+      <c r="D199" t="n">
+        <v>58.22000122070312</v>
+      </c>
+      <c r="E199" t="n">
+        <v>61.4900016784668</v>
+      </c>
+      <c r="F199" t="n">
+        <v>339103</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B200" t="n">
+        <v>59.4900016784668</v>
+      </c>
+      <c r="C200" t="n">
+        <v>60.16999816894531</v>
+      </c>
+      <c r="D200" t="n">
+        <v>59</v>
+      </c>
+      <c r="E200" t="n">
+        <v>59</v>
+      </c>
+      <c r="F200" t="n">
+        <v>339103</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B201" t="n">
+        <v>58.70000076293945</v>
+      </c>
+      <c r="C201" t="n">
+        <v>59.81999969482422</v>
+      </c>
+      <c r="D201" t="n">
+        <v>57.68000030517578</v>
+      </c>
+      <c r="E201" t="n">
+        <v>59.58000183105469</v>
+      </c>
+      <c r="F201" t="n">
+        <v>259200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B202" t="n">
+        <v>58.27000045776367</v>
+      </c>
+      <c r="C202" t="n">
+        <v>59.41999816894531</v>
+      </c>
+      <c r="D202" t="n">
+        <v>58.20000076293945</v>
+      </c>
+      <c r="E202" t="n">
+        <v>58.59999847412109</v>
+      </c>
+      <c r="F202" t="n">
+        <v>224919</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B203" t="n">
+        <v>57.45999908447266</v>
+      </c>
+      <c r="C203" t="n">
+        <v>59.11000061035156</v>
+      </c>
+      <c r="D203" t="n">
+        <v>57.2599983215332</v>
+      </c>
+      <c r="E203" t="n">
+        <v>58.77000045776367</v>
+      </c>
+      <c r="F203" t="n">
+        <v>203866</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B204" t="n">
+        <v>57.54000091552734</v>
+      </c>
+      <c r="C204" t="n">
+        <v>57.72000122070312</v>
+      </c>
+      <c r="D204" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="E204" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F204" t="n">
+        <v>108748</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B205" t="n">
+        <v>57.52000045776367</v>
+      </c>
+      <c r="C205" t="n">
+        <v>57.81000137329102</v>
+      </c>
+      <c r="D205" t="n">
+        <v>56.34999847412109</v>
+      </c>
+      <c r="E205" t="n">
+        <v>57.72999954223633</v>
+      </c>
+      <c r="F205" t="n">
+        <v>108146</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B206" t="n">
+        <v>57.81999969482422</v>
+      </c>
+      <c r="C206" t="n">
+        <v>58.27999877929688</v>
+      </c>
+      <c r="D206" t="n">
+        <v>56.9900016784668</v>
+      </c>
+      <c r="E206" t="n">
+        <v>57.36999893188477</v>
+      </c>
+      <c r="F206" t="n">
+        <v>314207</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B207" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C207" t="n">
+        <v>59.83000183105469</v>
+      </c>
+      <c r="D207" t="n">
+        <v>57.34000015258789</v>
+      </c>
+      <c r="E207" t="n">
+        <v>57.59000015258789</v>
+      </c>
+      <c r="F207" t="n">
+        <v>378637</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B208" t="n">
+        <v>61.79000091552734</v>
+      </c>
+      <c r="C208" t="n">
+        <v>62.20000076293945</v>
+      </c>
+      <c r="D208" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="E208" t="n">
+        <v>59.93999862670898</v>
+      </c>
+      <c r="F208" t="n">
+        <v>735186</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B209" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C209" t="n">
+        <v>62.59000015258789</v>
+      </c>
+      <c r="D209" t="n">
+        <v>61.20999908447266</v>
+      </c>
+      <c r="E209" t="n">
+        <v>61.79000091552734</v>
+      </c>
+      <c r="F209" t="n">
+        <v>373744</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B210" t="n">
+        <v>61.31000137329102</v>
+      </c>
+      <c r="C210" t="n">
+        <v>62.16999816894531</v>
+      </c>
+      <c r="D210" t="n">
+        <v>60.66999816894531</v>
+      </c>
+      <c r="E210" t="n">
+        <v>61.81999969482422</v>
+      </c>
+      <c r="F210" t="n">
+        <v>272191</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B211" t="n">
+        <v>60.15000152587891</v>
+      </c>
+      <c r="C211" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D211" t="n">
+        <v>59.7599983215332</v>
+      </c>
+      <c r="E211" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F211" t="n">
+        <v>307568</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B212" t="n">
+        <v>60.47999954223633</v>
+      </c>
+      <c r="C212" t="n">
+        <v>61.02000045776367</v>
+      </c>
+      <c r="D212" t="n">
+        <v>59.70000076293945</v>
+      </c>
+      <c r="E212" t="n">
+        <v>60.18000030517578</v>
+      </c>
+      <c r="F212" t="n">
+        <v>276875</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B213" t="n">
+        <v>60.56999969482422</v>
+      </c>
+      <c r="C213" t="n">
+        <v>60.79000091552734</v>
+      </c>
+      <c r="D213" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="E213" t="n">
+        <v>60.38999938964844</v>
+      </c>
+      <c r="F213" t="n">
+        <v>247917</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B214" t="n">
+        <v>60.97999954223633</v>
+      </c>
+      <c r="C214" t="n">
+        <v>61.38000106811523</v>
+      </c>
+      <c r="D214" t="n">
+        <v>59.9900016784668</v>
+      </c>
+      <c r="E214" t="n">
+        <v>60.29999923706055</v>
+      </c>
+      <c r="F214" t="n">
+        <v>278598</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B215" t="n">
+        <v>61.04999923706055</v>
+      </c>
+      <c r="C215" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>60.5099983215332</v>
+      </c>
+      <c r="E215" t="n">
+        <v>61.40000152587891</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B216" t="n">
+        <v>60.56000137329102</v>
+      </c>
+      <c r="C216" t="n">
+        <v>61.02999877929688</v>
+      </c>
+      <c r="D216" t="n">
+        <v>59.93999862670898</v>
+      </c>
+      <c r="E216" t="n">
+        <v>61.02999877929688</v>
+      </c>
+      <c r="F216" t="n">
+        <v>219300</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B217" t="n">
+        <v>59.59999847412109</v>
+      </c>
+      <c r="C217" t="n">
+        <v>61.09000015258789</v>
+      </c>
+      <c r="D217" t="n">
+        <v>59.52000045776367</v>
+      </c>
+      <c r="E217" t="n">
+        <v>60.43000030517578</v>
+      </c>
+      <c r="F217" t="n">
+        <v>292518</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B218" t="n">
+        <v>59.43000030517578</v>
+      </c>
+      <c r="C218" t="n">
+        <v>60.5099983215332</v>
+      </c>
+      <c r="D218" t="n">
+        <v>58.83000183105469</v>
+      </c>
+      <c r="E218" t="n">
+        <v>59.68000030517578</v>
+      </c>
+      <c r="F218" t="n">
+        <v>277768</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B219" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="C219" t="n">
+        <v>60.45999908447266</v>
+      </c>
+      <c r="D219" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="E219" t="n">
+        <v>59.65000152587891</v>
+      </c>
+      <c r="F219" t="n">
+        <v>259446</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B220" t="n">
+        <v>60.13000106811523</v>
+      </c>
+      <c r="C220" t="n">
+        <v>60.47999954223633</v>
+      </c>
+      <c r="D220" t="n">
+        <v>59.40999984741211</v>
+      </c>
+      <c r="E220" t="n">
+        <v>59.86999893188477</v>
+      </c>
+      <c r="F220" t="n">
+        <v>222879</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B221" t="n">
+        <v>61.04000091552734</v>
+      </c>
+      <c r="C221" t="n">
+        <v>61.27999877929688</v>
+      </c>
+      <c r="D221" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="E221" t="n">
+        <v>60.06999969482422</v>
+      </c>
+      <c r="F221" t="n">
+        <v>264427</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B222" t="n">
+        <v>58.4900016784668</v>
+      </c>
+      <c r="C222" t="n">
+        <v>61.06000137329102</v>
+      </c>
+      <c r="D222" t="n">
+        <v>58.29999923706055</v>
+      </c>
+      <c r="E222" t="n">
+        <v>61.04999923706055</v>
+      </c>
+      <c r="F222" t="n">
+        <v>329517</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B223" t="n">
+        <v>58.68999862670898</v>
+      </c>
+      <c r="C223" t="n">
+        <v>59.20999908447266</v>
+      </c>
+      <c r="D223" t="n">
+        <v>58.11999893188477</v>
+      </c>
+      <c r="E223" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="F223" t="n">
+        <v>247349</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B224" t="n">
+        <v>60.09000015258789</v>
+      </c>
+      <c r="C224" t="n">
+        <v>60.65000152587891</v>
+      </c>
+      <c r="D224" t="n">
+        <v>58.70999908447266</v>
+      </c>
+      <c r="E224" t="n">
+        <v>58.70999908447266</v>
+      </c>
+      <c r="F224" t="n">
+        <v>334116</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B225" t="n">
+        <v>59.90999984741211</v>
+      </c>
+      <c r="C225" t="n">
+        <v>60.43999862670898</v>
+      </c>
+      <c r="D225" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="E225" t="n">
+        <v>59.79999923706055</v>
+      </c>
+      <c r="F225" t="n">
+        <v>189638</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B226" t="n">
+        <v>60.7400016784668</v>
+      </c>
+      <c r="C226" t="n">
+        <v>60.93000030517578</v>
+      </c>
+      <c r="D226" t="n">
+        <v>59.31000137329102</v>
+      </c>
+      <c r="E226" t="n">
+        <v>59.7400016784668</v>
+      </c>
+      <c r="F226" t="n">
+        <v>105325</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B227" t="n">
+        <v>59.43999862670898</v>
+      </c>
+      <c r="C227" t="n">
+        <v>60.79000091552734</v>
+      </c>
+      <c r="D227" t="n">
+        <v>58.77000045776367</v>
+      </c>
+      <c r="E227" t="n">
+        <v>60.61999893188477</v>
+      </c>
+      <c r="F227" t="n">
+        <v>79622</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B228" t="n">
+        <v>59.13999938964844</v>
+      </c>
+      <c r="C228" t="n">
+        <v>60.33000183105469</v>
+      </c>
+      <c r="D228" t="n">
+        <v>58.86000061035156</v>
+      </c>
+      <c r="E228" t="n">
+        <v>59.63000106811523</v>
+      </c>
+      <c r="F228" t="n">
+        <v>324282</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B229" t="n">
+        <v>58.06000137329102</v>
+      </c>
+      <c r="C229" t="n">
+        <v>58.79999923706055</v>
+      </c>
+      <c r="D229" t="n">
+        <v>57.38000106811523</v>
+      </c>
+      <c r="E229" t="n">
+        <v>58.79999923706055</v>
+      </c>
+      <c r="F229" t="n">
+        <v>345014</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B230" t="n">
+        <v>58.84000015258789</v>
+      </c>
+      <c r="C230" t="n">
+        <v>59.06000137329102</v>
+      </c>
+      <c r="D230" t="n">
+        <v>57.41999816894531</v>
+      </c>
+      <c r="E230" t="n">
+        <v>58.04999923706055</v>
+      </c>
+      <c r="F230" t="n">
+        <v>238138</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B231" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="C231" t="n">
+        <v>58.95999908447266</v>
+      </c>
+      <c r="D231" t="n">
+        <v>57.09999847412109</v>
+      </c>
+      <c r="E231" t="n">
+        <v>58.88999938964844</v>
+      </c>
+      <c r="F231" t="n">
+        <v>334442</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B232" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="C232" t="n">
+        <v>58.72000122070312</v>
+      </c>
+      <c r="D232" t="n">
+        <v>57.65999984741211</v>
+      </c>
+      <c r="E232" t="n">
+        <v>58.04999923706055</v>
+      </c>
+      <c r="F232" t="n">
+        <v>228285</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B233" t="n">
+        <v>58.54999923706055</v>
+      </c>
+      <c r="C233" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="D233" t="n">
+        <v>58.27000045776367</v>
+      </c>
+      <c r="E233" t="n">
+        <v>58.58000183105469</v>
+      </c>
+      <c r="F233" t="n">
+        <v>153758</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B234" t="n">
+        <v>59.31999969482422</v>
+      </c>
+      <c r="C234" t="n">
+        <v>59.97000122070312</v>
+      </c>
+      <c r="D234" t="n">
+        <v>58.83000183105469</v>
+      </c>
+      <c r="E234" t="n">
+        <v>58.95999908447266</v>
+      </c>
+      <c r="F234" t="n">
+        <v>232770</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B235" t="n">
+        <v>58.63999938964844</v>
+      </c>
+      <c r="C235" t="n">
+        <v>59.66999816894531</v>
+      </c>
+      <c r="D235" t="n">
+        <v>58.27999877929688</v>
+      </c>
+      <c r="E235" t="n">
+        <v>59.52000045776367</v>
+      </c>
+      <c r="F235" t="n">
+        <v>255513</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B236" t="n">
+        <v>58.95000076293945</v>
+      </c>
+      <c r="C236" t="n">
+        <v>59.63999938964844</v>
+      </c>
+      <c r="D236" t="n">
+        <v>58.36999893188477</v>
+      </c>
+      <c r="E236" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="F236" t="n">
+        <v>260974</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B237" t="n">
+        <v>59.66999816894531</v>
+      </c>
+      <c r="C237" t="n">
+        <v>60.02000045776367</v>
+      </c>
+      <c r="D237" t="n">
+        <v>58.81000137329102</v>
+      </c>
+      <c r="E237" t="n">
+        <v>59.09000015258789</v>
+      </c>
+      <c r="F237" t="n">
+        <v>264993</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B238" t="n">
+        <v>60.08000183105469</v>
+      </c>
+      <c r="C238" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D238" t="n">
+        <v>59.41999816894531</v>
+      </c>
+      <c r="E238" t="n">
+        <v>59.70000076293945</v>
+      </c>
+      <c r="F238" t="n">
+        <v>255075</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B239" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="C239" t="n">
+        <v>60.29999923706055</v>
+      </c>
+      <c r="D239" t="n">
+        <v>58.68000030517578</v>
+      </c>
+      <c r="E239" t="n">
+        <v>60.15000152587891</v>
+      </c>
+      <c r="F239" t="n">
+        <v>263009</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B240" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="C240" t="n">
+        <v>59.16999816894531</v>
+      </c>
+      <c r="D240" t="n">
+        <v>58.11999893188477</v>
+      </c>
+      <c r="E240" t="n">
+        <v>58.86999893188477</v>
+      </c>
+      <c r="F240" t="n">
+        <v>260206</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B241" t="n">
+        <v>58.45999908447266</v>
+      </c>
+      <c r="C241" t="n">
+        <v>59.04999923706055</v>
+      </c>
+      <c r="D241" t="n">
+        <v>57.65999984741211</v>
+      </c>
+      <c r="E241" t="n">
+        <v>58.36999893188477</v>
+      </c>
+      <c r="F241" t="n">
+        <v>256508</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B242" t="n">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="C242" t="n">
+        <v>58.93999862670898</v>
+      </c>
+      <c r="D242" t="n">
+        <v>57.0099983215332</v>
+      </c>
+      <c r="E242" t="n">
+        <v>58.90999984741211</v>
+      </c>
+      <c r="F242" t="n">
+        <v>286808</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B243" t="n">
+        <v>57.43999862670898</v>
+      </c>
+      <c r="C243" t="n">
+        <v>58.18999862670898</v>
+      </c>
+      <c r="D243" t="n">
+        <v>57.15000152587891</v>
+      </c>
+      <c r="E243" t="n">
+        <v>57.88999938964844</v>
+      </c>
+      <c r="F243" t="n">
+        <v>212806</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B244" t="n">
+        <v>56.81999969482422</v>
+      </c>
+      <c r="C244" t="n">
+        <v>57.79999923706055</v>
+      </c>
+      <c r="D244" t="n">
+        <v>56.40000152587891</v>
+      </c>
+      <c r="E244" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F244" t="n">
+        <v>229310</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B245" t="n">
+        <v>55.27000045776367</v>
+      </c>
+      <c r="C245" t="n">
+        <v>56.70000076293945</v>
+      </c>
+      <c r="D245" t="n">
+        <v>54.97999954223633</v>
+      </c>
+      <c r="E245" t="n">
+        <v>56.68000030517578</v>
+      </c>
+      <c r="F245" t="n">
+        <v>230933</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B246" t="n">
+        <v>55.93999862670898</v>
+      </c>
+      <c r="C246" t="n">
+        <v>56.97999954223633</v>
+      </c>
+      <c r="D246" t="n">
+        <v>55.20000076293945</v>
+      </c>
+      <c r="E246" t="n">
+        <v>55.22999954223633</v>
+      </c>
+      <c r="F246" t="n">
+        <v>125608</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B247" t="n">
+        <v>56.15000152587891</v>
+      </c>
+      <c r="C247" t="n">
+        <v>57.02999877929688</v>
+      </c>
+      <c r="D247" t="n">
+        <v>55.88000106811523</v>
+      </c>
+      <c r="E247" t="n">
+        <v>56.90000152587891</v>
+      </c>
+      <c r="F247" t="n">
+        <v>85735</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B248" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="C248" t="n">
+        <v>56.90000152587891</v>
+      </c>
+      <c r="D248" t="n">
+        <v>55.81999969482422</v>
+      </c>
+      <c r="E248" t="n">
+        <v>56.02999877929688</v>
+      </c>
+      <c r="F248" t="n">
+        <v>209264</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B249" t="n">
+        <v>58.0099983215332</v>
+      </c>
+      <c r="C249" t="n">
+        <v>58.13000106811523</v>
+      </c>
+      <c r="D249" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="E249" t="n">
+        <v>56.63000106811523</v>
+      </c>
+      <c r="F249" t="n">
+        <v>221576</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B250" t="n">
+        <v>58.38000106811523</v>
+      </c>
+      <c r="C250" t="n">
+        <v>58.56000137329102</v>
+      </c>
+      <c r="D250" t="n">
+        <v>57.7400016784668</v>
+      </c>
+      <c r="E250" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F250" t="n">
+        <v>183633</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B251" t="n">
+        <v>58.34999847412109</v>
+      </c>
+      <c r="C251" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="D251" t="n">
+        <v>58.13000106811523</v>
+      </c>
+      <c r="E251" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="F251" t="n">
+        <v>111762</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B252" t="n">
+        <v>56.7400016784668</v>
+      </c>
+      <c r="C252" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="D252" t="n">
+        <v>56.65000152587891</v>
+      </c>
+      <c r="E252" t="n">
+        <v>58.34999847412109</v>
+      </c>
+      <c r="F252" t="n">
+        <v>166669</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B253" t="n">
+        <v>58.08000183105469</v>
+      </c>
+      <c r="C253" t="n">
+        <v>58.29999923706055</v>
+      </c>
+      <c r="D253" t="n">
+        <v>56.90999984741211</v>
+      </c>
+      <c r="E253" t="n">
+        <v>57.04000091552734</v>
+      </c>
+      <c r="F253" t="n">
+        <v>178590</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B254" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="C254" t="n">
+        <v>58.47000122070312</v>
+      </c>
+      <c r="D254" t="n">
+        <v>57.59999847412109</v>
+      </c>
+      <c r="E254" t="n">
+        <v>57.81000137329102</v>
+      </c>
+      <c r="F254" t="n">
+        <v>143802</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B255" t="n">
+        <v>57.41999816894531</v>
+      </c>
+      <c r="C255" t="n">
+        <v>58.54999923706055</v>
+      </c>
+      <c r="D255" t="n">
+        <v>57.20000076293945</v>
+      </c>
+      <c r="E255" t="n">
+        <v>57.95000076293945</v>
+      </c>
+      <c r="F255" t="n">
+        <v>157160</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B256" t="n">
+        <v>57.31999969482422</v>
+      </c>
+      <c r="C256" t="n">
+        <v>57.93000030517578</v>
+      </c>
+      <c r="D256" t="n">
+        <v>56.59999847412109</v>
+      </c>
+      <c r="E256" t="n">
+        <v>57.40999984741211</v>
+      </c>
+      <c r="F256" t="n">
+        <v>189503</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B257" t="n">
+        <v>58.31999969482422</v>
+      </c>
+      <c r="C257" t="n">
+        <v>58.5099983215332</v>
+      </c>
+      <c r="D257" t="n">
+        <v>56.31000137329102</v>
+      </c>
+      <c r="E257" t="n">
+        <v>57.47000122070312</v>
+      </c>
+      <c r="F257" t="n">
+        <v>301483</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B258" t="n">
+        <v>57.13000106811523</v>
+      </c>
+      <c r="C258" t="n">
+        <v>58.86999893188477</v>
+      </c>
+      <c r="D258" t="n">
+        <v>56.84000015258789</v>
+      </c>
+      <c r="E258" t="n">
+        <v>58.34000015258789</v>
+      </c>
+      <c r="F258" t="n">
+        <v>292067</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B259" t="n">
+        <v>55.9900016784668</v>
+      </c>
+      <c r="C259" t="n">
+        <v>57.16999816894531</v>
+      </c>
+      <c r="D259" t="n">
+        <v>55.7599983215332</v>
+      </c>
+      <c r="E259" t="n">
+        <v>57</v>
+      </c>
+      <c r="F259" t="n">
+        <v>383128</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B260" t="n">
+        <v>57.7599983215332</v>
+      </c>
+      <c r="C260" t="n">
+        <v>58.7400016784668</v>
+      </c>
+      <c r="D260" t="n">
+        <v>55.97000122070312</v>
+      </c>
+      <c r="E260" t="n">
+        <v>56.41999816894531</v>
+      </c>
+      <c r="F260" t="n">
+        <v>334134</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B261" t="n">
+        <v>59.11999893188477</v>
+      </c>
+      <c r="C261" t="n">
+        <v>59.77000045776367</v>
+      </c>
+      <c r="D261" t="n">
+        <v>57.61000061035156</v>
+      </c>
+      <c r="E261" t="n">
+        <v>58.40000152587891</v>
+      </c>
+      <c r="F261" t="n">
+        <v>360309</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B262" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="C262" t="n">
+        <v>59.90999984741211</v>
+      </c>
+      <c r="D262" t="n">
+        <v>58.45000076293945</v>
+      </c>
+      <c r="E262" t="n">
+        <v>59</v>
+      </c>
+      <c r="F262" t="n">
+        <v>309700</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B263" t="n">
+        <v>61.15000152587891</v>
+      </c>
+      <c r="C263" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D263" t="n">
+        <v>59.47000122070312</v>
+      </c>
+      <c r="E263" t="n">
+        <v>59.95000076293945</v>
+      </c>
+      <c r="F263" t="n">
+        <v>411190</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B264" t="n">
+        <v>62.02000045776367</v>
+      </c>
+      <c r="C264" t="n">
+        <v>62.36000061035156</v>
+      </c>
+      <c r="D264" t="n">
+        <v>59.18999862670898</v>
+      </c>
+      <c r="E264" t="n">
+        <v>61.11999893188477</v>
+      </c>
+      <c r="F264" t="n">
+        <v>410261</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B265" t="n">
+        <v>59.18999862670898</v>
+      </c>
+      <c r="C265" t="n">
+        <v>61.13999938964844</v>
+      </c>
+      <c r="D265" t="n">
+        <v>58.88000106811523</v>
+      </c>
+      <c r="E265" t="n">
+        <v>61.06000137329102</v>
+      </c>
+      <c r="F265" t="n">
+        <v>113642</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B266" t="n">
+        <v>59.43999862670898</v>
+      </c>
+      <c r="C266" t="n">
+        <v>60.18000030517578</v>
+      </c>
+      <c r="D266" t="n">
+        <v>58.93999862670898</v>
+      </c>
+      <c r="E266" t="n">
+        <v>59.2599983215332</v>
+      </c>
+      <c r="F266" t="n">
+        <v>113794</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B267" t="n">
+        <v>60.34000015258789</v>
+      </c>
+      <c r="C267" t="n">
+        <v>60.68000030517578</v>
+      </c>
+      <c r="D267" t="n">
+        <v>58.70000076293945</v>
+      </c>
+      <c r="E267" t="n">
+        <v>59.0099983215332</v>
+      </c>
+      <c r="F267" t="n">
+        <v>499595</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B268" t="n">
+        <v>60.61999893188477</v>
+      </c>
+      <c r="C268" t="n">
+        <v>60.88999938964844</v>
+      </c>
+      <c r="D268" t="n">
+        <v>59.22000122070312</v>
+      </c>
+      <c r="E268" t="n">
+        <v>59.56999969482422</v>
+      </c>
+      <c r="F268" t="n">
+        <v>333062</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B269" t="n">
+        <v>59.36000061035156</v>
+      </c>
+      <c r="C269" t="n">
+        <v>60.81999969482422</v>
+      </c>
+      <c r="D269" t="n">
+        <v>58.95999908447266</v>
+      </c>
+      <c r="E269" t="n">
+        <v>60.68000030517578</v>
+      </c>
+      <c r="F269" t="n">
+        <v>324349</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B270" t="n">
+        <v>61.06999969482422</v>
+      </c>
+      <c r="C270" t="n">
+        <v>61.36000061035156</v>
+      </c>
+      <c r="D270" t="n">
+        <v>59.52000045776367</v>
+      </c>
+      <c r="E270" t="n">
+        <v>59.65999984741211</v>
+      </c>
+      <c r="F270" t="n">
+        <v>283419</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B271" t="n">
+        <v>60.63000106811523</v>
+      </c>
+      <c r="C271" t="n">
+        <v>61.70999908447266</v>
+      </c>
+      <c r="D271" t="n">
+        <v>60.31999969482422</v>
+      </c>
+      <c r="E271" t="n">
+        <v>61.22000122070312</v>
+      </c>
+      <c r="F271" t="n">
+        <v>281062</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B272" t="n">
+        <v>62.38999938964844</v>
+      </c>
+      <c r="C272" t="n">
+        <v>62.63000106811523</v>
+      </c>
+      <c r="D272" t="n">
+        <v>60.13999938964844</v>
+      </c>
+      <c r="E272" t="n">
+        <v>60.77999877929688</v>
+      </c>
+      <c r="F272" t="n">
+        <v>360208</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B273" t="n">
+        <v>63.20999908447266</v>
+      </c>
+      <c r="C273" t="n">
+        <v>63.56999969482422</v>
+      </c>
+      <c r="D273" t="n">
+        <v>62.06999969482422</v>
+      </c>
+      <c r="E273" t="n">
+        <v>62.58000183105469</v>
+      </c>
+      <c r="F273" t="n">
+        <v>354864</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B274" t="n">
+        <v>65.41999816894531</v>
+      </c>
+      <c r="C274" t="n">
+        <v>66.48000335693359</v>
+      </c>
+      <c r="D274" t="n">
+        <v>63.27999877929688</v>
+      </c>
+      <c r="E274" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F274" t="n">
+        <v>560007</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B275" t="n">
         <v>65.20999908447266</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C275" t="n">
         <v>66.11000061035156</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D275" t="n">
         <v>63.63999938964844</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E275" t="n">
         <v>65.51999664306641</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F275" t="n">
         <v>560007</v>
       </c>
     </row>
